--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Corporate Bond Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Corporate Bond Fund.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OPERAT\Factsheet 2013-14\January 2025\ISIN Port 310125_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OPERAT\Factsheet 2013-14\May 2025\ISIN Portfolios 310525\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="CORPORATE BOND" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="316">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -27,7 +27,7 @@
     <t>ICICI Prudential Corporate Bond Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -78,13 +78,40 @@
     <t>IN0020200120</t>
   </si>
   <si>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
     <t>IN0020210137</t>
   </si>
   <si>
-    <t>IN0020230085</t>
-  </si>
-  <si>
-    <t>IN0020240126</t>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>State Government of Chhattisgarh</t>
+  </si>
+  <si>
+    <t>IN3520240083</t>
+  </si>
+  <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
   </si>
   <si>
     <t>State Government of Rajasthan</t>
@@ -99,28 +126,43 @@
     <t>IN1220150024</t>
   </si>
   <si>
-    <t>State Government of Maharashtra</t>
-  </si>
-  <si>
     <t>IN2220150139</t>
   </si>
   <si>
+    <t>IN2920150454</t>
+  </si>
+  <si>
     <t>IN0020240134</t>
   </si>
   <si>
-    <t>IN2920150454</t>
+    <t>^</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
     <t>NABARD</t>
   </si>
   <si>
     <t>INE261F08DX0</t>
   </si>
   <si>
-    <t>CRISIL AAA</t>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08EM1</t>
+  </si>
+  <si>
+    <t>ICRA AAA</t>
   </si>
   <si>
     <t>Pipeline Infrastructure Pvt Ltd. **</t>
@@ -135,10 +177,19 @@
     <t>INE029A08073</t>
   </si>
   <si>
-    <t>INE261F08EM1</t>
-  </si>
-  <si>
-    <t>ICRA AAA</t>
+    <t>INE115A07QC7</t>
+  </si>
+  <si>
+    <t>Rural Electrification Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE020B08EM0</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE134E08MO2</t>
   </si>
   <si>
     <t>Small Industries Development Bank Of India. **</t>
@@ -147,46 +198,496 @@
     <t>INE556F08KD0</t>
   </si>
   <si>
-    <t>LIC Housing Finance Ltd. **</t>
+    <t>Titan Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE280A08015</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE040A08AF2</t>
+  </si>
+  <si>
+    <t>INE261F08EF5</t>
+  </si>
+  <si>
+    <t>INE261F08DW2</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E08NL6</t>
+  </si>
+  <si>
+    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE128M08078</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(CE)</t>
+  </si>
+  <si>
+    <t>Jamnagar Utilities &amp; Power Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE936D07190</t>
+  </si>
+  <si>
+    <t>Summit Digitel Infrastructure Private Ltd. **</t>
+  </si>
+  <si>
+    <t>INE507T07146</t>
+  </si>
+  <si>
+    <t>INE556F08KJ7</t>
+  </si>
+  <si>
+    <t>INE261F08EA6</t>
+  </si>
+  <si>
+    <t>INE556F08KU4</t>
+  </si>
+  <si>
+    <t>INE020B08EP3</t>
+  </si>
+  <si>
+    <t>INE556F08KG3</t>
+  </si>
+  <si>
+    <t>Citicorp Finance (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE915D08CX8</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India.</t>
+  </si>
+  <si>
+    <t>INE556F08KX8</t>
+  </si>
+  <si>
+    <t>INE556F08KI9</t>
+  </si>
+  <si>
+    <t>INE115A07RB7</t>
+  </si>
+  <si>
+    <t>INE936D07182</t>
+  </si>
+  <si>
+    <t>INE134E08NP7</t>
+  </si>
+  <si>
+    <t>Tata Capital Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE033L07IE2</t>
+  </si>
+  <si>
+    <t>Nexus Select Trust **</t>
+  </si>
+  <si>
+    <t>INE0NDH07050</t>
+  </si>
+  <si>
+    <t>INE134E08LZ0</t>
+  </si>
+  <si>
+    <t>INE115A07QV7</t>
+  </si>
+  <si>
+    <t>INE033L07IN3</t>
+  </si>
+  <si>
+    <t>Summit Digitel Infrastructure Ltd **</t>
+  </si>
+  <si>
+    <t>INE507T07062</t>
+  </si>
+  <si>
+    <t>INE115A07MW4</t>
+  </si>
+  <si>
+    <t>INE556F08KT6</t>
+  </si>
+  <si>
+    <t>INE115A07QW5</t>
+  </si>
+  <si>
+    <t>State Bank of India ( Tier II Bond under Basel III ) **</t>
+  </si>
+  <si>
+    <t>INE062A08256</t>
+  </si>
+  <si>
+    <t>Sikka Ports &amp; Terminals Ltd. **</t>
+  </si>
+  <si>
+    <t>INE941D07208</t>
+  </si>
+  <si>
+    <t>Mahanagar Telephone Nigam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE153A08170</t>
+  </si>
+  <si>
+    <t>FITCH AAA(CE)</t>
+  </si>
+  <si>
+    <t>INE020B08ED9</t>
+  </si>
+  <si>
+    <t>INE134E08LP1</t>
+  </si>
+  <si>
+    <t>INE915D08CY6</t>
+  </si>
+  <si>
+    <t>INE153A08089</t>
+  </si>
+  <si>
+    <t>BWR AA+(CE)</t>
+  </si>
+  <si>
+    <t>INE556F08KH1</t>
+  </si>
+  <si>
+    <t>DME Development Ltd. **</t>
+  </si>
+  <si>
+    <t>INE0J7Q07249</t>
+  </si>
+  <si>
+    <t>Dabur India Ltd. **</t>
+  </si>
+  <si>
+    <t>INE016A08021</t>
+  </si>
+  <si>
+    <t>INE020B08EL2</t>
+  </si>
+  <si>
+    <t>INE020B08EF4</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Investments Ltd. **</t>
+  </si>
+  <si>
+    <t>INE975F07ID8</t>
+  </si>
+  <si>
+    <t>SMFG India Credit Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE535H07CG2</t>
+  </si>
+  <si>
+    <t>INE556F08KP4</t>
+  </si>
+  <si>
+    <t>INE115A07NP6</t>
+  </si>
+  <si>
+    <t>Kohima-Mariani Transmission Ltd. **</t>
+  </si>
+  <si>
+    <t>INE483Z08012</t>
+  </si>
+  <si>
+    <t>FITCH AAA</t>
   </si>
   <si>
     <t>INE115A07NU6</t>
   </si>
   <si>
-    <t>INE115A07QC7</t>
-  </si>
-  <si>
-    <t>Titan Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE280A08015</t>
-  </si>
-  <si>
-    <t>Rural Electrification Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE020B08EM0</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE134E08MO2</t>
-  </si>
-  <si>
-    <t>INE556F08KA6</t>
-  </si>
-  <si>
-    <t>INE261F08EF5</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F08DT8</t>
-  </si>
-  <si>
-    <t>INE261F08DW2</t>
+    <t>INE261F08EB4</t>
+  </si>
+  <si>
+    <t>INE261F08EO7</t>
+  </si>
+  <si>
+    <t>SMFG India Home Finance Company Ltd **</t>
+  </si>
+  <si>
+    <t>INE213W07319</t>
+  </si>
+  <si>
+    <t>CARE AAA</t>
+  </si>
+  <si>
+    <t>INE062A08264</t>
+  </si>
+  <si>
+    <t>INE01XX07059</t>
+  </si>
+  <si>
+    <t>Housing and Urban Development Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE031A08871</t>
+  </si>
+  <si>
+    <t>INE115A07PV9</t>
+  </si>
+  <si>
+    <t>INE556F08KM1</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd. **</t>
+  </si>
+  <si>
+    <t>INE775A08089</t>
+  </si>
+  <si>
+    <t>INE115A07QN4</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.( Tier II Bond under Basel III ) **</t>
+  </si>
+  <si>
+    <t>INE040A08435</t>
+  </si>
+  <si>
+    <t>INE556F08KL3</t>
+  </si>
+  <si>
+    <t>INE775A08097</t>
+  </si>
+  <si>
+    <t>INE115A07QX3</t>
+  </si>
+  <si>
+    <t>INE507T07112</t>
+  </si>
+  <si>
+    <t>INE261F08ED0</t>
+  </si>
+  <si>
+    <t>Aditya Birla Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE831R07425</t>
+  </si>
+  <si>
+    <t>INE033L07IK9</t>
+  </si>
+  <si>
+    <t>INE134E08MC7</t>
+  </si>
+  <si>
+    <t>INE115A07KM9</t>
+  </si>
+  <si>
+    <t>INE556F08KF5</t>
+  </si>
+  <si>
+    <t>INE556F08KE8</t>
+  </si>
+  <si>
+    <t>INE040A08914</t>
+  </si>
+  <si>
+    <t>ICICI Home Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE071G07843</t>
+  </si>
+  <si>
+    <t>INE071G07777</t>
+  </si>
+  <si>
+    <t>INE020B08DT7</t>
+  </si>
+  <si>
+    <t>SMFG India Credit Company Ltd **</t>
+  </si>
+  <si>
+    <t>INE535H07CK4</t>
+  </si>
+  <si>
+    <t>INE556F08KN9</t>
+  </si>
+  <si>
+    <t>INE040A08427</t>
+  </si>
+  <si>
+    <t>INE033L07HZ9</t>
+  </si>
+  <si>
+    <t>INE115A07QH6</t>
+  </si>
+  <si>
+    <t>INE062A08447</t>
+  </si>
+  <si>
+    <t>INE556F08KW0</t>
+  </si>
+  <si>
+    <t>INE115A07LO3</t>
+  </si>
+  <si>
+    <t>SMFG India Home Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE213W07293</t>
+  </si>
+  <si>
+    <t>EMBASSY OFFICE PARKS REIT **</t>
+  </si>
+  <si>
+    <t>INE041007175</t>
+  </si>
+  <si>
+    <t>INE115A07PF2</t>
+  </si>
+  <si>
+    <t>Bharat Sanchar Nigam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE103D08054</t>
+  </si>
+  <si>
+    <t>INE020B08EK4</t>
+  </si>
+  <si>
+    <t>INE0J7Q07017</t>
+  </si>
+  <si>
+    <t>INE020B08AH8</t>
+  </si>
+  <si>
+    <t>INE261F08EI9</t>
+  </si>
+  <si>
+    <t>INE020B08FA2</t>
+  </si>
+  <si>
+    <t>INE0J7Q07108</t>
+  </si>
+  <si>
+    <t>INE020B08EW9</t>
+  </si>
+  <si>
+    <t>INE0J7Q07074</t>
+  </si>
+  <si>
+    <t>INE0J7Q07090</t>
+  </si>
+  <si>
+    <t>INE0J7Q07082</t>
+  </si>
+  <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
+    <t>INE0J7Q07066</t>
+  </si>
+  <si>
+    <t>INE0J7Q07041</t>
+  </si>
+  <si>
+    <t>INE134E08ML8</t>
+  </si>
+  <si>
+    <t>Rural Electrification Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE020B08EI8</t>
+  </si>
+  <si>
+    <t>INE031A08855</t>
+  </si>
+  <si>
+    <t>Sundaram Home Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE667F07JA5</t>
+  </si>
+  <si>
+    <t>INE041007167</t>
+  </si>
+  <si>
+    <t>INE915D08CV2</t>
+  </si>
+  <si>
+    <t>INE020B08DH2</t>
+  </si>
+  <si>
+    <t>INE01XX07042</t>
+  </si>
+  <si>
+    <t>INE020B08FF1</t>
+  </si>
+  <si>
+    <t>INE020B08ES7</t>
+  </si>
+  <si>
+    <t>INE941D07158</t>
+  </si>
+  <si>
+    <t>INE134E08II2</t>
+  </si>
+  <si>
+    <t>HDB Financial Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE756I07EM6</t>
+  </si>
+  <si>
+    <t>INE134E08LX5</t>
+  </si>
+  <si>
+    <t>Nomura Capital (India) Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE357L07481</t>
+  </si>
+  <si>
+    <t>INE041007142</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A08807</t>
+  </si>
+  <si>
+    <t>INE115A07PN6</t>
+  </si>
+  <si>
+    <t>Nomura Fixed Income Securities Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE127K08017</t>
+  </si>
+  <si>
+    <t>INE115A07JT6</t>
+  </si>
+  <si>
+    <t>INE115A07MC6</t>
+  </si>
+  <si>
+    <t>INE134E08IE1</t>
+  </si>
+  <si>
+    <t>INE040A08484</t>
+  </si>
+  <si>
+    <t>INE261F08DO9</t>
+  </si>
+  <si>
+    <t>INE115A07QD5</t>
   </si>
   <si>
     <t>Bajaj Finance Ltd. **</t>
@@ -195,507 +696,48 @@
     <t>INE296A07SF4</t>
   </si>
   <si>
-    <t>Summit Digitel Infrastructure Private Ltd. **</t>
-  </si>
-  <si>
-    <t>INE507T07146</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A08AF2</t>
-  </si>
-  <si>
-    <t>INE261F08EA6</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India.</t>
-  </si>
-  <si>
-    <t>INE556F08KJ7</t>
-  </si>
-  <si>
-    <t>INE020B08EP3</t>
-  </si>
-  <si>
-    <t>INE556F08KG3</t>
-  </si>
-  <si>
-    <t>Citicorp Finance (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE915D08CX8</t>
-  </si>
-  <si>
-    <t>Tata Capital Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE033L07IE2</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E08LO4</t>
-  </si>
-  <si>
-    <t>INE556F08KE8</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Financial Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE774D07VC5</t>
-  </si>
-  <si>
-    <t>INE556F08KI9</t>
-  </si>
-  <si>
-    <t>INE115A07MW4</t>
-  </si>
-  <si>
-    <t>INE774D07UI4</t>
-  </si>
-  <si>
-    <t>FITCH AAA</t>
-  </si>
-  <si>
-    <t>INE280A08023</t>
-  </si>
-  <si>
-    <t>L&amp;T Metro Rail (Hyderabad) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE128M08078</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(CE)</t>
-  </si>
-  <si>
-    <t>Jamnagar Utilities &amp; Power Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE936D07182</t>
-  </si>
-  <si>
-    <t>INE115A07RB7</t>
-  </si>
-  <si>
-    <t>INE134E08LZ0</t>
-  </si>
-  <si>
-    <t>Axis Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE891K07770</t>
-  </si>
-  <si>
-    <t>Summit Digitel Infrastructure Ltd **</t>
-  </si>
-  <si>
-    <t>INE507T07062</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A07QV7</t>
-  </si>
-  <si>
-    <t>INE556F08KT6</t>
-  </si>
-  <si>
-    <t>INE134E08LD7</t>
-  </si>
-  <si>
-    <t>State Bank of India ( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE062A08256</t>
-  </si>
-  <si>
-    <t>Sikka Ports &amp; Terminals Ltd. **</t>
-  </si>
-  <si>
-    <t>INE941D07208</t>
-  </si>
-  <si>
-    <t>INE020B08DF6</t>
-  </si>
-  <si>
-    <t>INE020B08ED9</t>
-  </si>
-  <si>
-    <t>INE134E08KT5</t>
-  </si>
-  <si>
-    <t>Mahanagar Telephone Nigam Ltd.</t>
-  </si>
-  <si>
-    <t>INE153A08170</t>
-  </si>
-  <si>
-    <t>FITCH AAA(CE)</t>
-  </si>
-  <si>
-    <t>INE915D08CY6</t>
-  </si>
-  <si>
-    <t>INE153A08089</t>
-  </si>
-  <si>
-    <t>BWR AA+(CE)</t>
-  </si>
-  <si>
-    <t>DME Development Ltd. **</t>
-  </si>
-  <si>
-    <t>INE0J7Q07249</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Investments Ltd. **</t>
-  </si>
-  <si>
-    <t>INE975F07ID8</t>
-  </si>
-  <si>
-    <t>SMFG India Credit Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE535H07CG2</t>
-  </si>
-  <si>
-    <t>INE020B08EF4</t>
-  </si>
-  <si>
-    <t>INE020B08EL2</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd. **</t>
-  </si>
-  <si>
-    <t>INE016A08021</t>
-  </si>
-  <si>
-    <t>INE134E08LP1</t>
-  </si>
-  <si>
-    <t>Kohima-Mariani Transmission Ltd. **</t>
-  </si>
-  <si>
-    <t>INE483Z08012</t>
-  </si>
-  <si>
-    <t>INE115A07NP6</t>
-  </si>
-  <si>
-    <t>INE062A08264</t>
-  </si>
-  <si>
-    <t>INE01XX07059</t>
-  </si>
-  <si>
-    <t>Housing and Urban Development Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE031A08871</t>
-  </si>
-  <si>
-    <t>INE115A07PV9</t>
-  </si>
-  <si>
-    <t>Samvardhana Motherson International Ltd. **</t>
-  </si>
-  <si>
-    <t>INE775A08089</t>
-  </si>
-  <si>
-    <t>INE556F08KH1</t>
-  </si>
-  <si>
-    <t>INE115A07QN4</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE040A08435</t>
-  </si>
-  <si>
-    <t>INE507T07112</t>
-  </si>
-  <si>
-    <t>Aditya Birla Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE831R07425</t>
-  </si>
-  <si>
-    <t>INE261F08ED0</t>
-  </si>
-  <si>
-    <t>INE115A07QX3</t>
-  </si>
-  <si>
-    <t>INE134E08MC7</t>
-  </si>
-  <si>
-    <t>INE115A07KM9</t>
-  </si>
-  <si>
-    <t>INE033L07IK9</t>
-  </si>
-  <si>
-    <t>Nomura Capital (India) Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE357L07440</t>
-  </si>
-  <si>
-    <t>INE774D07VB7</t>
-  </si>
-  <si>
-    <t>ICICI Home Finance Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE071G07777</t>
-  </si>
-  <si>
-    <t>INE134E08MN4</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A08922</t>
-  </si>
-  <si>
-    <t>INE556F08KF5</t>
+    <t>Jio Credit Ltd **</t>
+  </si>
+  <si>
+    <t>INE282H07018</t>
   </si>
   <si>
     <t>Kotak Mahindra Prime Ltd. **</t>
   </si>
   <si>
-    <t>INE916DA7RR2</t>
-  </si>
-  <si>
-    <t>SMFG India Credit Company Ltd **</t>
-  </si>
-  <si>
-    <t>INE535H07CK4</t>
-  </si>
-  <si>
-    <t>INE033L07HZ9</t>
-  </si>
-  <si>
-    <t>INE040A08427</t>
-  </si>
-  <si>
-    <t>INE115A07QH6</t>
-  </si>
-  <si>
-    <t>INE062A08447</t>
-  </si>
-  <si>
-    <t>INE115A07LO3</t>
-  </si>
-  <si>
-    <t>SMFG India Home Finance Co Ltd **</t>
-  </si>
-  <si>
-    <t>INE213W07236</t>
-  </si>
-  <si>
-    <t>CARE AAA</t>
-  </si>
-  <si>
-    <t>SMFG India Home Finance Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE213W07293</t>
-  </si>
-  <si>
-    <t>INE115A07PF2</t>
-  </si>
-  <si>
-    <t>INE261F08EB4</t>
-  </si>
-  <si>
-    <t>INE0J7Q07017</t>
-  </si>
-  <si>
-    <t>INE0J7Q07108</t>
-  </si>
-  <si>
-    <t>INE0J7Q07074</t>
-  </si>
-  <si>
-    <t>INE0J7Q07082</t>
-  </si>
-  <si>
-    <t>INE0J7Q07090</t>
-  </si>
-  <si>
-    <t>Bharat Sanchar Nigam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE103D08054</t>
-  </si>
-  <si>
-    <t>INE0J7Q07066</t>
-  </si>
-  <si>
-    <t>INE020B08AH8</t>
-  </si>
-  <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
-    <t>INE261F08EI9</t>
-  </si>
-  <si>
-    <t>INE020B08EW9</t>
-  </si>
-  <si>
-    <t>INE031A08855</t>
-  </si>
-  <si>
-    <t>INE0J7Q07041</t>
-  </si>
-  <si>
-    <t>INE916DA7RZ5</t>
-  </si>
-  <si>
-    <t>INE115A07QE3</t>
-  </si>
-  <si>
-    <t>INE915D08CV2</t>
-  </si>
-  <si>
-    <t>INE134E08ML8</t>
+    <t>INE916DA7RU6</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
   </si>
   <si>
     <t>INE774D07VA9</t>
   </si>
   <si>
-    <t>INE020B08EK4</t>
-  </si>
-  <si>
-    <t>INE020B08EI8</t>
-  </si>
-  <si>
-    <t>INE115A07MC6</t>
-  </si>
-  <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
-    <t>Rural Electrification Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE020B08DH2</t>
-  </si>
-  <si>
-    <t>HDB Financial Services Ltd. **</t>
+    <t>INE936D07174</t>
+  </si>
+  <si>
+    <t>INE115A07PI6</t>
   </si>
   <si>
     <t>INE756I07DX5</t>
   </si>
   <si>
-    <t>INE040A08914</t>
-  </si>
-  <si>
-    <t>INE01XX07042</t>
-  </si>
-  <si>
-    <t>INE020B08FF1</t>
-  </si>
-  <si>
-    <t>INE020B08ES7</t>
-  </si>
-  <si>
-    <t>INE941D07158</t>
-  </si>
-  <si>
-    <t>INE134E08II2</t>
-  </si>
-  <si>
-    <t>INE756I07EM6</t>
-  </si>
-  <si>
-    <t>INE115A07PZ0</t>
-  </si>
-  <si>
-    <t>INE357L07481</t>
-  </si>
-  <si>
-    <t>EMBASSY OFFICE PARKS REIT **</t>
-  </si>
-  <si>
-    <t>INE041007142</t>
-  </si>
-  <si>
-    <t>INE134E08LX5</t>
-  </si>
-  <si>
-    <t>INE115A07PN6</t>
-  </si>
-  <si>
-    <t>INE115A07JT6</t>
-  </si>
-  <si>
-    <t>Nomura Fixed Income Securities Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE127K08017</t>
-  </si>
-  <si>
-    <t>INE556F08KU4</t>
-  </si>
-  <si>
-    <t>INE020B08930</t>
-  </si>
-  <si>
-    <t>INE040A08484</t>
-  </si>
-  <si>
-    <t>INE115A07QB9</t>
-  </si>
-  <si>
-    <t>INE115A07QD5</t>
-  </si>
-  <si>
-    <t>INE916DA7RU6</t>
-  </si>
-  <si>
-    <t>INE128M08060</t>
-  </si>
-  <si>
-    <t>INE936D07174</t>
-  </si>
-  <si>
-    <t>INE115A07PI6</t>
+    <t>INE115A07RC5</t>
   </si>
   <si>
     <t>INE115A07IF7</t>
   </si>
   <si>
-    <t>INE261F08DR2</t>
+    <t>INE556F08KQ2</t>
+  </si>
+  <si>
+    <t>INE556F08KK5</t>
   </si>
   <si>
     <t>INE115A07HT0</t>
   </si>
   <si>
-    <t>INE134E08IE1</t>
-  </si>
-  <si>
-    <t>INE020B08963</t>
-  </si>
-  <si>
     <t>Larsen &amp; Toubro Ltd. **</t>
   </si>
   <si>
@@ -708,31 +750,37 @@
     <t>INE047A08208</t>
   </si>
   <si>
+    <t>INE071G07728</t>
+  </si>
+  <si>
     <t>INE040A08823</t>
   </si>
   <si>
     <t>INE020B08AC9</t>
   </si>
   <si>
-    <t>INE134E08LR7</t>
-  </si>
-  <si>
     <t>INE134E08IX1</t>
   </si>
   <si>
+    <t>Indian Railway Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE053F08338</t>
+  </si>
+  <si>
     <t>INE115A07QR5</t>
   </si>
   <si>
-    <t>INE040A08641</t>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E08FG5</t>
   </si>
   <si>
     <t>INE261F08DH3</t>
   </si>
   <si>
-    <t>^</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd. **</t>
+    <t>Hindustan Petroleum Corporation Ltd.</t>
   </si>
   <si>
     <t>INE094A08150</t>
@@ -780,6 +828,48 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
+    <t>INE514E16CL5</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
+  </si>
+  <si>
+    <t>Canara Bank</t>
+  </si>
+  <si>
+    <t>INE476A16B64</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238AD6918</t>
+  </si>
+  <si>
+    <t>Union Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE692A16ID1</t>
+  </si>
+  <si>
+    <t>ICRA A1+</t>
+  </si>
+  <si>
+    <t>Canara Bank **</t>
+  </si>
+  <si>
+    <t>INE476A16ZP7</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda **</t>
+  </si>
+  <si>
+    <t>INE028A16GQ4</t>
+  </si>
+  <si>
+    <t>FITCH A1+</t>
+  </si>
+  <si>
     <t>Commercial Papers</t>
   </si>
   <si>
@@ -810,6 +900,36 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -06-Mar-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -06-Mar-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -25-Apr-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> ICICI Securities Primary Dealership Ltd.- MD -25-Apr-2028 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -828,7 +948,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -841,9 +961,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY Corporate Bond Index A-II</t>
   </si>
   <si>
     <t>Mahanagar Telephone Nigam Ltd. ** #</t>
@@ -948,7 +1065,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1042,6 +1159,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1051,8 +1177,19 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -1064,17 +1201,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1124,6 +1250,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -1156,13 +1283,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>222</xdr:row>
+      <xdr:row>252</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>232</xdr:row>
+      <xdr:row>262</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1180,8 +1307,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="43205400"/>
-          <a:ext cx="3705225" cy="1905000"/>
+          <a:off x="666750" y="48682275"/>
+          <a:ext cx="5715000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1197,13 +1324,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>237</xdr:row>
+      <xdr:row>267</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>247</xdr:row>
+      <xdr:row>277</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1221,8 +1348,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="46062900"/>
-          <a:ext cx="3705225" cy="1905000"/>
+          <a:off x="666750" y="51539775"/>
+          <a:ext cx="5715000" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1557,59 +1684,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J236"/>
+  <dimension ref="A1:J265"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="27" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="55.5546875" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.33203125" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.6640625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="19.6640625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.5546875" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="38.6640625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.6640625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.6640625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.6640625" style="27" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="28" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="85.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.33203125" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="19.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.5546875" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="38.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1657,10 +1784,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="13">
-        <v>2797594.0299999984</v>
+        <v>2967895.6300000004</v>
       </c>
       <c r="H5" s="14">
-        <v>0.96026513286729942</v>
+        <v>0.94931239141509915</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>13</v>
@@ -1694,10 +1821,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="13">
-        <v>2680145.1299999985</v>
+        <v>2861833.9400000004</v>
       </c>
       <c r="H7" s="14">
-        <v>0.91995117653379932</v>
+        <v>0.91538745296579926</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>13</v>
@@ -1731,10 +1858,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="13">
-        <v>569095.02</v>
+        <v>625750.43999999994</v>
       </c>
       <c r="H9" s="14">
-        <v>0.19534003116150001</v>
+        <v>0.20015280881989997</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>13</v>
@@ -1757,16 +1884,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="19">
-        <v>290127880</v>
+        <v>202411180</v>
       </c>
       <c r="G10" s="20">
-        <v>297109.52</v>
+        <v>213377.82</v>
       </c>
       <c r="H10" s="21">
-        <v>0.1019818850204</v>
+        <v>6.8251122624800001E-2</v>
       </c>
       <c r="I10" s="20">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>13</v>
@@ -1780,22 +1907,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="18">
-        <v>7.9300000000000006</v>
+        <v>7.81</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="19">
-        <v>200204630</v>
+        <v>195495560</v>
       </c>
       <c r="G11" s="20">
-        <v>205333.07</v>
+        <v>203010.8</v>
       </c>
       <c r="H11" s="21">
-        <v>7.0479914395300006E-2</v>
+        <v>6.4935123083400006E-2</v>
       </c>
       <c r="I11" s="20">
-        <v>7.66</v>
+        <v>7.31</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>13</v>
@@ -1809,22 +1936,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="18">
-        <v>7.53</v>
+        <v>6.79</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="19">
-        <v>38217650</v>
+        <v>62850810</v>
       </c>
       <c r="G12" s="20">
-        <v>38496.14</v>
+        <v>65108.98</v>
       </c>
       <c r="H12" s="21">
-        <v>1.32136759643E-2</v>
+        <v>2.08257867568E-2</v>
       </c>
       <c r="I12" s="20">
-        <v>7.47</v>
+        <v>6.37</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>13</v>
@@ -1838,22 +1965,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="18">
-        <v>7.18</v>
+        <v>7.34</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="19">
-        <v>18546460</v>
+        <v>58412000</v>
       </c>
       <c r="G13" s="20">
-        <v>19053.61</v>
+        <v>62175.72</v>
       </c>
       <c r="H13" s="21">
-        <v>6.5400902140000002E-3</v>
+        <v>1.9887552933099999E-2</v>
       </c>
       <c r="I13" s="20">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>13</v>
@@ -1867,22 +1994,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="18">
-        <v>6.79</v>
+        <v>6.99</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="19">
-        <v>5971600</v>
+        <v>29217650</v>
       </c>
       <c r="G14" s="20">
-        <v>6010.99</v>
+        <v>29824.33</v>
       </c>
       <c r="H14" s="21">
-        <v>2.0632529413E-3</v>
+        <v>9.5396232092999998E-3</v>
       </c>
       <c r="I14" s="20">
-        <v>6.81</v>
+        <v>6.8</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>13</v>
@@ -1896,22 +2023,22 @@
         <v>23</v>
       </c>
       <c r="D15" s="18">
-        <v>8.39</v>
+        <v>7.12</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="19">
-        <v>1425000</v>
+        <v>14882100</v>
       </c>
       <c r="G15" s="20">
-        <v>1446.43</v>
+        <v>15382.72</v>
       </c>
       <c r="H15" s="21">
-        <v>4.9648243490000004E-4</v>
+        <v>4.9203235323E-3</v>
       </c>
       <c r="I15" s="20">
-        <v>7.08</v>
+        <v>6.83</v>
       </c>
       <c r="J15" s="15" t="s">
         <v>13</v>
@@ -1919,28 +2046,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>25</v>
-      </c>
       <c r="D16" s="18">
-        <v>8.43</v>
+        <v>7.1400000000000006</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="19">
-        <v>500000</v>
+        <v>14000000</v>
       </c>
       <c r="G16" s="20">
-        <v>507.68</v>
+        <v>14528.57</v>
       </c>
       <c r="H16" s="21">
-        <v>1.7425952350000001E-4</v>
+        <v>4.6471147404999998E-3</v>
       </c>
       <c r="I16" s="20">
-        <v>6.91</v>
+        <v>6.82</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>13</v>
@@ -1948,28 +2075,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>27</v>
-      </c>
       <c r="D17" s="18">
-        <v>8.15</v>
+        <v>7.32</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="19">
-        <v>500000</v>
+        <v>11051200</v>
       </c>
       <c r="G17" s="20">
-        <v>505.33</v>
+        <v>11599.64</v>
       </c>
       <c r="H17" s="21">
-        <v>1.734528935E-4</v>
+        <v>3.7102659125E-3</v>
       </c>
       <c r="I17" s="20">
-        <v>6.88</v>
+        <v>6.81</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>13</v>
@@ -1977,28 +2104,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="18">
-        <v>6.92</v>
+        <v>7.13</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="19">
-        <v>345400</v>
+        <v>5657700</v>
       </c>
       <c r="G18" s="20">
-        <v>348.45</v>
+        <v>5844.12</v>
       </c>
       <c r="H18" s="21">
-        <v>1.196043392E-4</v>
+        <v>1.8693027736E-3</v>
       </c>
       <c r="I18" s="20">
-        <v>6.94</v>
+        <v>6.75</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>13</v>
@@ -2006,28 +2133,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D19" s="18">
-        <v>8.2100000000000009</v>
+        <v>7.29</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="19">
-        <v>280000</v>
+        <v>2021800</v>
       </c>
       <c r="G19" s="20">
-        <v>283.8</v>
+        <v>2110.48</v>
       </c>
       <c r="H19" s="21">
-        <v>9.7413435099999999E-5</v>
+        <v>6.7505905380000003E-4</v>
       </c>
       <c r="I19" s="20">
-        <v>7.08</v>
+        <v>6.88</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>13</v>
@@ -2035,36 +2162,57 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="18">
+        <v>8.39</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="19">
+        <v>1425000</v>
+      </c>
+      <c r="G20" s="20">
+        <v>1450.75</v>
+      </c>
+      <c r="H20" s="21">
+        <v>4.6403752810000003E-4</v>
+      </c>
+      <c r="I20" s="20">
+        <v>6.08</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="13">
-        <v>2111050.1100000003</v>
-      </c>
-      <c r="H21" s="14">
-        <v>0.72461114537229976</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>13</v>
+      <c r="B21" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="18">
+        <v>8.43</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="19">
+        <v>500000</v>
+      </c>
+      <c r="G21" s="20">
+        <v>508.16</v>
+      </c>
+      <c r="H21" s="21">
+        <v>1.6254027930000001E-4</v>
+      </c>
+      <c r="I21" s="20">
+        <v>5.92</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>13</v>
@@ -2072,28 +2220,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D22" s="18">
-        <v>7.58</v>
+        <v>8.15</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F22" s="19">
-        <v>96500</v>
+        <v>500000</v>
       </c>
       <c r="G22" s="20">
-        <v>96367.02</v>
+        <v>505.5</v>
       </c>
       <c r="H22" s="21">
-        <v>3.3077668980099999E-2</v>
+        <v>1.6168945060000001E-4</v>
       </c>
       <c r="I22" s="20">
-        <v>7.63</v>
+        <v>5.8</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>13</v>
@@ -2101,28 +2249,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="18">
-        <v>7.96</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F23" s="19">
-        <v>80500</v>
+        <v>280000</v>
       </c>
       <c r="G23" s="20">
-        <v>81406.83</v>
+        <v>284.79000000000002</v>
       </c>
       <c r="H23" s="21">
-        <v>2.7942631986099999E-2</v>
+        <v>9.1093053599999998E-5</v>
       </c>
       <c r="I23" s="20">
-        <v>7.84</v>
+        <v>6.14</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>13</v>
@@ -2130,28 +2278,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="16" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D24" s="18">
-        <v>7.58</v>
+        <v>6.92</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F24" s="19">
-        <v>59000</v>
+        <v>36350</v>
       </c>
       <c r="G24" s="20">
-        <v>59084.08</v>
-      </c>
-      <c r="H24" s="21">
-        <v>2.0280420005000001E-2</v>
+        <v>38.06</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="I24" s="20">
-        <v>7.42</v>
+        <v>6.52</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>13</v>
@@ -2159,57 +2307,36 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="18">
-        <v>7.53</v>
-      </c>
-      <c r="E25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="19">
-        <v>58050</v>
-      </c>
-      <c r="G25" s="20">
-        <v>58119.02</v>
-      </c>
-      <c r="H25" s="21">
-        <v>1.9949166270800001E-2</v>
-      </c>
-      <c r="I25" s="20">
-        <v>7.5</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="18">
-        <v>7.75</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="19">
-        <v>5250</v>
-      </c>
-      <c r="G26" s="20">
-        <v>52440.31</v>
-      </c>
-      <c r="H26" s="21">
-        <v>1.79999673684E-2</v>
-      </c>
-      <c r="I26" s="20">
-        <v>7.84</v>
+      <c r="C26" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="13">
+        <v>2236083.5000000014</v>
+      </c>
+      <c r="H26" s="14">
+        <v>0.71523464414589932</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J26" s="15" t="s">
         <v>13</v>
@@ -2217,28 +2344,28 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D27" s="18">
-        <v>8.8000000000000007</v>
+        <v>7.58</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F27" s="19">
-        <v>5000</v>
+        <v>108500</v>
       </c>
       <c r="G27" s="20">
-        <v>51893.7</v>
+        <v>111212.61</v>
       </c>
       <c r="H27" s="21">
-        <v>1.7812345247899999E-2</v>
+        <v>3.5572513968599999E-2</v>
       </c>
       <c r="I27" s="20">
-        <v>7.66</v>
+        <v>7.21</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>13</v>
@@ -2246,28 +2373,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>44</v>
       </c>
       <c r="D28" s="18">
-        <v>7.8</v>
+        <v>7.58</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F28" s="19">
-        <v>5000</v>
+        <v>106500</v>
       </c>
       <c r="G28" s="20">
-        <v>50110.9</v>
+        <v>107574.9</v>
       </c>
       <c r="H28" s="21">
-        <v>1.7200404894700001E-2</v>
+        <v>3.4408954460400001E-2</v>
       </c>
       <c r="I28" s="20">
-        <v>7.7</v>
+        <v>6.62</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>13</v>
@@ -2281,22 +2408,22 @@
         <v>46</v>
       </c>
       <c r="D29" s="18">
-        <v>7.75</v>
+        <v>7.53</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F29" s="19">
-        <v>48000</v>
+        <v>95550</v>
       </c>
       <c r="G29" s="20">
-        <v>47956.37</v>
+        <v>97704.84</v>
       </c>
       <c r="H29" s="21">
-        <v>1.64608694172E-2</v>
+        <v>3.1251912761500002E-2</v>
       </c>
       <c r="I29" s="20">
-        <v>7.73</v>
+        <v>6.61</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>13</v>
@@ -2304,28 +2431,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D30" s="18">
-        <v>7.6400000000000006</v>
+        <v>7.96</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F30" s="19">
-        <v>47500</v>
+        <v>80500</v>
       </c>
       <c r="G30" s="20">
-        <v>47476.92</v>
+        <v>83426.98</v>
       </c>
       <c r="H30" s="21">
-        <v>1.62962997502E-2</v>
+        <v>2.6684990230899999E-2</v>
       </c>
       <c r="I30" s="20">
-        <v>7.63</v>
+        <v>6.98</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>13</v>
@@ -2333,28 +2460,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D31" s="18">
-        <v>7.37</v>
+        <v>7.58</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F31" s="19">
-        <v>47500</v>
+        <v>59000</v>
       </c>
       <c r="G31" s="20">
-        <v>47319.360000000001</v>
+        <v>59477.49</v>
       </c>
       <c r="H31" s="21">
-        <v>1.6242217788100002E-2</v>
+        <v>1.9024495907800001E-2</v>
       </c>
       <c r="I31" s="20">
-        <v>7.64</v>
+        <v>6.41</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>13</v>
@@ -2365,25 +2492,25 @@
         <v>40</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D32" s="18">
-        <v>7.25</v>
+        <v>7.8</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F32" s="19">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="G32" s="20">
-        <v>45827.55</v>
+        <v>51049.65</v>
       </c>
       <c r="H32" s="21">
-        <v>1.57301588143E-2</v>
+        <v>1.6328763327399999E-2</v>
       </c>
       <c r="I32" s="20">
-        <v>7.75</v>
+        <v>6.85</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>13</v>
@@ -2391,28 +2518,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="16" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D33" s="18">
-        <v>7.8</v>
+        <v>7.6400000000000006</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F33" s="19">
-        <v>40000</v>
+        <v>47500</v>
       </c>
       <c r="G33" s="20">
-        <v>40181.68</v>
+        <v>48012.29</v>
       </c>
       <c r="H33" s="21">
-        <v>1.3792232136100001E-2</v>
+        <v>1.53572320323E-2</v>
       </c>
       <c r="I33" s="20">
-        <v>7.54</v>
+        <v>6.56</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>13</v>
@@ -2420,28 +2547,28 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" s="18">
-        <v>7.5</v>
+        <v>7.37</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F34" s="19">
-        <v>3975</v>
+        <v>47500</v>
       </c>
       <c r="G34" s="20">
-        <v>39642.32</v>
+        <v>47850.41</v>
       </c>
       <c r="H34" s="21">
-        <v>1.3607098554699999E-2</v>
+        <v>1.5305453024800001E-2</v>
       </c>
       <c r="I34" s="20">
-        <v>7.75</v>
+        <v>6.55</v>
       </c>
       <c r="J34" s="15" t="s">
         <v>13</v>
@@ -2449,28 +2576,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D35" s="18">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F35" s="19">
-        <v>35000</v>
+        <v>4600</v>
       </c>
       <c r="G35" s="20">
-        <v>34947.22</v>
+        <v>46160.26</v>
       </c>
       <c r="H35" s="21">
-        <v>1.1995520614100001E-2</v>
+        <v>1.4764840908199999E-2</v>
       </c>
       <c r="I35" s="20">
-        <v>7.69</v>
+        <v>6.72</v>
       </c>
       <c r="J35" s="15" t="s">
         <v>13</v>
@@ -2478,28 +2605,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D36" s="18">
-        <v>7.9</v>
+        <v>7.75</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F36" s="19">
-        <v>3000</v>
+        <v>43000</v>
       </c>
       <c r="G36" s="20">
-        <v>29968.68</v>
+        <v>43142.720000000001</v>
       </c>
       <c r="H36" s="21">
-        <v>1.02866528072E-2</v>
+        <v>1.3799649246999999E-2</v>
       </c>
       <c r="I36" s="20">
-        <v>7.91</v>
+        <v>6.65</v>
       </c>
       <c r="J36" s="15" t="s">
         <v>13</v>
@@ -2507,28 +2634,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D37" s="18">
-        <v>7.87</v>
+        <v>7.75</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F37" s="19">
-        <v>28300</v>
+        <v>40000</v>
       </c>
       <c r="G37" s="20">
-        <v>28502.63</v>
+        <v>41732.04</v>
       </c>
       <c r="H37" s="21">
-        <v>9.7834358705000003E-3</v>
+        <v>1.3348428526500001E-2</v>
       </c>
       <c r="I37" s="20">
-        <v>7.92</v>
+        <v>7.03</v>
       </c>
       <c r="J37" s="15" t="s">
         <v>13</v>
@@ -2536,28 +2663,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="16" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D38" s="18">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F38" s="19">
-        <v>27500</v>
+        <v>40000</v>
       </c>
       <c r="G38" s="20">
-        <v>28041.7</v>
+        <v>40786.04</v>
       </c>
       <c r="H38" s="21">
-        <v>9.6252231337999993E-3</v>
+        <v>1.30458405537E-2</v>
       </c>
       <c r="I38" s="20">
-        <v>7.42</v>
+        <v>6.57</v>
       </c>
       <c r="J38" s="15" t="s">
         <v>13</v>
@@ -2565,28 +2692,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="16" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D39" s="18">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F39" s="19">
-        <v>27500</v>
+        <v>35000</v>
       </c>
       <c r="G39" s="20">
-        <v>27434.17</v>
+        <v>35230.300000000003</v>
       </c>
       <c r="H39" s="21">
-        <v>9.4166904196000007E-3</v>
+        <v>1.12687791327E-2</v>
       </c>
       <c r="I39" s="20">
-        <v>7.62</v>
+        <v>6.6</v>
       </c>
       <c r="J39" s="15" t="s">
         <v>13</v>
@@ -2594,28 +2721,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D40" s="18">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F40" s="19">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="G40" s="20">
-        <v>26958.69</v>
+        <v>30649.71</v>
       </c>
       <c r="H40" s="21">
-        <v>9.2534834423000003E-3</v>
+        <v>9.8036296163000001E-3</v>
       </c>
       <c r="I40" s="20">
-        <v>7.61</v>
+        <v>6.56</v>
       </c>
       <c r="J40" s="15" t="s">
         <v>13</v>
@@ -2623,28 +2750,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="16" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D41" s="18">
-        <v>7.77</v>
+        <v>6.58</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="F41" s="19">
-        <v>26500</v>
+        <v>3050</v>
       </c>
       <c r="G41" s="20">
-        <v>26549.03</v>
+        <v>30430.77</v>
       </c>
       <c r="H41" s="21">
-        <v>9.1128689677999995E-3</v>
+        <v>9.7335993724000005E-3</v>
       </c>
       <c r="I41" s="20">
-        <v>7.61</v>
+        <v>6.81</v>
       </c>
       <c r="J41" s="15" t="s">
         <v>13</v>
@@ -2652,28 +2779,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D42" s="18">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F42" s="19">
-        <v>25500</v>
+        <v>29500</v>
       </c>
       <c r="G42" s="20">
-        <v>25462.52</v>
+        <v>29918.87</v>
       </c>
       <c r="H42" s="21">
-        <v>8.7399279126000005E-3</v>
+        <v>9.5698628149999999E-3</v>
       </c>
       <c r="I42" s="20">
-        <v>7.75</v>
+        <v>7.21</v>
       </c>
       <c r="J42" s="15" t="s">
         <v>13</v>
@@ -2681,28 +2808,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D43" s="18">
-        <v>8.43</v>
+        <v>7.87</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F43" s="19">
-        <v>25500</v>
+        <v>28300</v>
       </c>
       <c r="G43" s="20">
-        <v>25462.11</v>
+        <v>29308.19</v>
       </c>
       <c r="H43" s="21">
-        <v>8.7397871814999997E-3</v>
+        <v>9.3745304436999993E-3</v>
       </c>
       <c r="I43" s="20">
-        <v>9.1</v>
+        <v>7.15</v>
       </c>
       <c r="J43" s="15" t="s">
         <v>13</v>
@@ -2710,28 +2837,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D44" s="18">
-        <v>8.1</v>
+        <v>7.55</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F44" s="19">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="G44" s="20">
-        <v>25149.65</v>
+        <v>28305.96</v>
       </c>
       <c r="H44" s="21">
-        <v>8.6325362936999998E-3</v>
+        <v>9.0539567184999992E-3</v>
       </c>
       <c r="I44" s="20">
-        <v>7.77</v>
+        <v>6.61</v>
       </c>
       <c r="J44" s="15" t="s">
         <v>13</v>
@@ -2739,28 +2866,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="16" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D45" s="18">
-        <v>7.13</v>
+        <v>7.5</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F45" s="19">
-        <v>2350</v>
+        <v>27500</v>
       </c>
       <c r="G45" s="20">
-        <v>23393.4</v>
+        <v>27769.45</v>
       </c>
       <c r="H45" s="21">
-        <v>8.0297091422999994E-3</v>
+        <v>8.8823483957000005E-3</v>
       </c>
       <c r="I45" s="20">
-        <v>7.78</v>
+        <v>6.62</v>
       </c>
       <c r="J45" s="15" t="s">
         <v>13</v>
@@ -2768,28 +2895,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="16" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D46" s="18">
-        <v>7.47</v>
+        <v>7.51</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F46" s="19">
-        <v>2250</v>
+        <v>26500</v>
       </c>
       <c r="G46" s="20">
-        <v>22427.75</v>
+        <v>27144.880000000001</v>
       </c>
       <c r="H46" s="21">
-        <v>7.6982528926E-3</v>
+        <v>8.6825731629999996E-3</v>
       </c>
       <c r="I46" s="20">
-        <v>7.84</v>
+        <v>6.59</v>
       </c>
       <c r="J46" s="15" t="s">
         <v>13</v>
@@ -2797,28 +2924,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="16" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D47" s="18">
-        <v>7.9585000000000008</v>
+        <v>7.77</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F47" s="19">
-        <v>21500</v>
+        <v>26500</v>
       </c>
       <c r="G47" s="20">
-        <v>21469.88</v>
+        <v>26885.31</v>
       </c>
       <c r="H47" s="21">
-        <v>7.3694671026999998E-3</v>
+        <v>8.5995469895000006E-3</v>
       </c>
       <c r="I47" s="20">
-        <v>7.97</v>
+        <v>6.55</v>
       </c>
       <c r="J47" s="15" t="s">
         <v>13</v>
@@ -2826,28 +2953,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D48" s="18">
-        <v>7.44</v>
+        <v>7.59</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F48" s="19">
-        <v>21500</v>
+        <v>25500</v>
       </c>
       <c r="G48" s="20">
-        <v>21433.01</v>
+        <v>25655.68</v>
       </c>
       <c r="H48" s="21">
-        <v>7.3568115940999997E-3</v>
+        <v>8.2062370011000002E-3</v>
       </c>
       <c r="I48" s="20">
-        <v>7.61</v>
+        <v>6.6</v>
       </c>
       <c r="J48" s="15" t="s">
         <v>13</v>
@@ -2855,28 +2982,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="16" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D49" s="18">
-        <v>7.95</v>
+        <v>7.76</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F49" s="19">
-        <v>2100</v>
+        <v>25500</v>
       </c>
       <c r="G49" s="20">
-        <v>21162.5</v>
+        <v>25506.09</v>
       </c>
       <c r="H49" s="21">
-        <v>7.2639599086000003E-3</v>
+        <v>8.1583890784000003E-3</v>
       </c>
       <c r="I49" s="20">
-        <v>7.65</v>
+        <v>7.56</v>
       </c>
       <c r="J49" s="15" t="s">
         <v>13</v>
@@ -2884,28 +3011,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="16" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D50" s="18">
-        <v>8.11</v>
+        <v>7.49</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="F50" s="19">
-        <v>2100</v>
+        <v>22500</v>
       </c>
       <c r="G50" s="20">
-        <v>21000.11</v>
+        <v>23149.82</v>
       </c>
       <c r="H50" s="21">
-        <v>7.2082200645000004E-3</v>
+        <v>7.4047115279000002E-3</v>
       </c>
       <c r="I50" s="20">
-        <v>7.78</v>
+        <v>6.65</v>
       </c>
       <c r="J50" s="15" t="s">
         <v>13</v>
@@ -2913,28 +3040,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D51" s="18">
-        <v>7.75</v>
+        <v>7.44</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F51" s="19">
-        <v>20500</v>
+        <v>21500</v>
       </c>
       <c r="G51" s="20">
-        <v>20494.240000000002</v>
+        <v>21699.54</v>
       </c>
       <c r="H51" s="21">
-        <v>7.0345818177000004E-3</v>
+        <v>6.9408243342000001E-3</v>
       </c>
       <c r="I51" s="20">
-        <v>7.72</v>
+        <v>6.61</v>
       </c>
       <c r="J51" s="15" t="s">
         <v>13</v>
@@ -2942,28 +3069,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D52" s="18">
-        <v>6.58</v>
+        <v>7.58</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F52" s="19">
-        <v>2050</v>
+        <v>20000</v>
       </c>
       <c r="G52" s="20">
-        <v>20185.59</v>
+        <v>20586.52</v>
       </c>
       <c r="H52" s="21">
-        <v>6.9286387000999997E-3</v>
+        <v>6.5848132713E-3</v>
       </c>
       <c r="I52" s="20">
-        <v>7.89</v>
+        <v>7.14</v>
       </c>
       <c r="J52" s="15" t="s">
         <v>13</v>
@@ -2971,7 +3098,7 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="16" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>85</v>
@@ -2980,19 +3107,19 @@
         <v>7.9</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F53" s="19">
         <v>20000</v>
       </c>
       <c r="G53" s="20">
-        <v>20146.919999999998</v>
+        <v>20576.28</v>
       </c>
       <c r="H53" s="21">
-        <v>6.9153653472000002E-3</v>
+        <v>6.5815379004000004E-3</v>
       </c>
       <c r="I53" s="20">
-        <v>7.63</v>
+        <v>6.85</v>
       </c>
       <c r="J53" s="15" t="s">
         <v>13</v>
@@ -3000,28 +3127,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="16" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>86</v>
       </c>
       <c r="D54" s="18">
-        <v>7.58</v>
+        <v>7.45</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F54" s="19">
         <v>20000</v>
       </c>
       <c r="G54" s="20">
-        <v>20080.66</v>
+        <v>20494.38</v>
       </c>
       <c r="H54" s="21">
-        <v>6.8926218158000003E-3</v>
+        <v>6.5553413305999998E-3</v>
       </c>
       <c r="I54" s="20">
-        <v>7.52</v>
+        <v>6.55</v>
       </c>
       <c r="J54" s="15" t="s">
         <v>13</v>
@@ -3029,28 +3156,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D55" s="18">
-        <v>7.58</v>
+        <v>8.1</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F55" s="19">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="G55" s="20">
-        <v>19973.68</v>
+        <v>20339.599999999999</v>
       </c>
       <c r="H55" s="21">
-        <v>6.8559012757000003E-3</v>
+        <v>6.5058333322999999E-3</v>
       </c>
       <c r="I55" s="20">
-        <v>7.72</v>
+        <v>6.99</v>
       </c>
       <c r="J55" s="15" t="s">
         <v>13</v>
@@ -3058,28 +3185,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D56" s="18">
-        <v>6.75</v>
+        <v>7.19</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F56" s="19">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="G56" s="20">
-        <v>19918</v>
+        <v>20121.82</v>
       </c>
       <c r="H56" s="21">
-        <v>6.8367892951000002E-3</v>
+        <v>6.4361741264999999E-3</v>
       </c>
       <c r="I56" s="20">
-        <v>7.98</v>
+        <v>7.08</v>
       </c>
       <c r="J56" s="15" t="s">
         <v>13</v>
@@ -3087,28 +3214,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>91</v>
       </c>
       <c r="D57" s="18">
-        <v>6.59</v>
+        <v>7.58</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F57" s="19">
         <v>2000</v>
       </c>
       <c r="G57" s="20">
-        <v>19723.419999999998</v>
+        <v>20114.919999999998</v>
       </c>
       <c r="H57" s="21">
-        <v>6.7700003374000003E-3</v>
+        <v>6.4339670894999999E-3</v>
       </c>
       <c r="I57" s="20">
-        <v>7.89</v>
+        <v>6.53</v>
       </c>
       <c r="J57" s="15" t="s">
         <v>13</v>
@@ -3116,28 +3243,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="17" t="s">
         <v>92</v>
-      </c>
-      <c r="C58" s="17" t="s">
-        <v>93</v>
       </c>
       <c r="D58" s="18">
         <v>7.61</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F58" s="19">
         <v>19500</v>
       </c>
       <c r="G58" s="20">
-        <v>19629.77</v>
+        <v>20095.61</v>
       </c>
       <c r="H58" s="21">
-        <v>6.7378552766999998E-3</v>
+        <v>6.4277905843999998E-3</v>
       </c>
       <c r="I58" s="20">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="J58" s="15" t="s">
         <v>13</v>
@@ -3145,28 +3272,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59" s="18">
-        <v>7.44</v>
+        <v>7.27</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F59" s="19">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="G59" s="20">
-        <v>18983.11</v>
+        <v>20089.5</v>
       </c>
       <c r="H59" s="21">
-        <v>6.5158913162000004E-3</v>
+        <v>6.4258362372E-3</v>
       </c>
       <c r="I59" s="20">
-        <v>7.47</v>
+        <v>7.09</v>
       </c>
       <c r="J59" s="15" t="s">
         <v>13</v>
@@ -3174,28 +3301,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>95</v>
       </c>
       <c r="D60" s="18">
-        <v>6.5</v>
+        <v>6.59</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F60" s="19">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G60" s="20">
-        <v>18833.64</v>
+        <v>19982.599999999999</v>
       </c>
       <c r="H60" s="21">
-        <v>6.4645862204999998E-3</v>
+        <v>6.3916431565000003E-3</v>
       </c>
       <c r="I60" s="20">
-        <v>7.78</v>
+        <v>6.85</v>
       </c>
       <c r="J60" s="15" t="s">
         <v>13</v>
@@ -3203,57 +3330,57 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C61" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="D61" s="18">
-        <v>6.24</v>
+        <v>7.95</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F61" s="19">
-        <v>1815</v>
+        <v>1900</v>
       </c>
       <c r="G61" s="20">
-        <v>17966.990000000002</v>
+        <v>19452.62</v>
       </c>
       <c r="H61" s="21">
-        <v>6.1671114016000001E-3</v>
+        <v>6.2221235224000004E-3</v>
       </c>
       <c r="I61" s="20">
-        <v>6.45</v>
-      </c>
-      <c r="J61" s="15">
-        <v>7.74</v>
+        <v>6.92</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="16" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D62" s="18">
-        <v>6.75</v>
+        <v>7.44</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F62" s="19">
-        <v>1800</v>
+        <v>19000</v>
       </c>
       <c r="G62" s="20">
-        <v>17783.14</v>
+        <v>19405.21</v>
       </c>
       <c r="H62" s="21">
-        <v>6.1040054818000001E-3</v>
+        <v>6.2069589391000003E-3</v>
       </c>
       <c r="I62" s="20">
-        <v>7.79</v>
+        <v>6.59</v>
       </c>
       <c r="J62" s="15" t="s">
         <v>13</v>
@@ -3261,28 +3388,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="16" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D63" s="18">
-        <v>5.85</v>
+        <v>7.74</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F63" s="19">
-        <v>1800</v>
+        <v>18500</v>
       </c>
       <c r="G63" s="20">
-        <v>17714.02</v>
+        <v>18854.37</v>
       </c>
       <c r="H63" s="21">
-        <v>6.0802802646000003E-3</v>
+        <v>6.0307670162999998E-3</v>
       </c>
       <c r="I63" s="20">
-        <v>7.72</v>
+        <v>6.92</v>
       </c>
       <c r="J63" s="15" t="s">
         <v>13</v>
@@ -3290,57 +3417,57 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="16" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D64" s="18">
-        <v>7.56</v>
+        <v>6.24</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F64" s="19">
-        <v>17500</v>
+        <v>1815</v>
       </c>
       <c r="G64" s="20">
-        <v>17473.580000000002</v>
+        <v>18162.759999999998</v>
       </c>
       <c r="H64" s="21">
-        <v>5.9977500096000001E-3</v>
+        <v>5.8095483399E-3</v>
       </c>
       <c r="I64" s="20">
-        <v>7.63</v>
-      </c>
-      <c r="J64" s="15" t="s">
-        <v>13</v>
+        <v>6.22</v>
+      </c>
+      <c r="J64" s="15">
+        <v>5.76</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="16" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>102</v>
       </c>
       <c r="D65" s="18">
-        <v>7.17</v>
+        <v>6.75</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F65" s="19">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G65" s="20">
-        <v>17454.97</v>
+        <v>17996.259999999998</v>
       </c>
       <c r="H65" s="21">
-        <v>5.9913621870999996E-3</v>
+        <v>5.7562915772999997E-3</v>
       </c>
       <c r="I65" s="20">
-        <v>7.66</v>
+        <v>6.73</v>
       </c>
       <c r="J65" s="15" t="s">
         <v>13</v>
@@ -3363,13 +3490,13 @@
         <v>17500</v>
       </c>
       <c r="G66" s="20">
-        <v>17268.04</v>
+        <v>17749.52</v>
       </c>
       <c r="H66" s="21">
-        <v>5.9271990672000001E-3</v>
+        <v>5.6773692132E-3</v>
       </c>
       <c r="I66" s="20">
-        <v>8.17</v>
+        <v>7.71</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>13</v>
@@ -3377,28 +3504,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="16" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>106</v>
       </c>
       <c r="D67" s="18">
-        <v>8.3000000000000007</v>
+        <v>7.56</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F67" s="19">
-        <v>17000</v>
+        <v>17500</v>
       </c>
       <c r="G67" s="20">
-        <v>16956.45</v>
+        <v>17674.63</v>
       </c>
       <c r="H67" s="21">
-        <v>5.8202468041000004E-3</v>
+        <v>5.6534148651000002E-3</v>
       </c>
       <c r="I67" s="20">
-        <v>9.09</v>
+        <v>6.56</v>
       </c>
       <c r="J67" s="15" t="s">
         <v>13</v>
@@ -3406,28 +3533,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="16" t="s">
-        <v>275</v>
+        <v>65</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>107</v>
       </c>
       <c r="D68" s="18">
-        <v>7.05</v>
+        <v>7.13</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="F68" s="19">
-        <v>1667</v>
+        <v>1750</v>
       </c>
       <c r="G68" s="20">
-        <v>15987.25</v>
+        <v>17602.919999999998</v>
       </c>
       <c r="H68" s="21">
-        <v>5.4875720282000001E-3</v>
+        <v>5.6304776732000001E-3</v>
       </c>
       <c r="I68" s="20">
-        <v>8.11</v>
+        <v>6.55</v>
       </c>
       <c r="J68" s="15" t="s">
         <v>13</v>
@@ -3435,28 +3562,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="16" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D69" s="18">
-        <v>7.55</v>
+        <v>8.3500000000000014</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F69" s="19">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="G69" s="20">
-        <v>15306.71</v>
+        <v>16993.099999999999</v>
       </c>
       <c r="H69" s="21">
-        <v>5.2539788669E-3</v>
+        <v>5.4354203819000002E-3</v>
       </c>
       <c r="I69" s="20">
-        <v>7.45</v>
+        <v>7.9</v>
       </c>
       <c r="J69" s="15" t="s">
         <v>13</v>
@@ -3464,28 +3591,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="16" t="s">
-        <v>111</v>
+        <v>314</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D70" s="18">
-        <v>8.1577000000000002</v>
+        <v>7.05</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="F70" s="19">
-        <v>15000</v>
+        <v>1667</v>
       </c>
       <c r="G70" s="20">
-        <v>15034.5</v>
+        <v>16435.09</v>
       </c>
       <c r="H70" s="21">
-        <v>5.1605436619000002E-3</v>
+        <v>5.2569350597000001E-3</v>
       </c>
       <c r="I70" s="20">
-        <v>7.91</v>
+        <v>7.51</v>
       </c>
       <c r="J70" s="15" t="s">
         <v>13</v>
@@ -3493,28 +3620,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="16" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D71" s="18">
-        <v>8.3000000000000007</v>
+        <v>7.43</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F71" s="19">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="G71" s="20">
-        <v>14989.56</v>
+        <v>16145.54</v>
       </c>
       <c r="H71" s="21">
-        <v>5.1451181518000003E-3</v>
+        <v>5.1643194703999999E-3</v>
       </c>
       <c r="I71" s="20">
-        <v>8.16</v>
+        <v>6.61</v>
       </c>
       <c r="J71" s="15" t="s">
         <v>13</v>
@@ -3522,28 +3649,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="16" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D72" s="18">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F72" s="19">
         <v>15000</v>
       </c>
       <c r="G72" s="20">
-        <v>14989.02</v>
+        <v>15692.1</v>
       </c>
       <c r="H72" s="21">
-        <v>5.1449327985000001E-3</v>
+        <v>5.0192819541E-3</v>
       </c>
       <c r="I72" s="20">
-        <v>7.66</v>
+        <v>7.14</v>
       </c>
       <c r="J72" s="15" t="s">
         <v>13</v>
@@ -3551,28 +3678,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="18">
+        <v>7.35</v>
+      </c>
+      <c r="E73" s="17" t="s">
         <v>47</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" s="18">
-        <v>7.44</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>33</v>
       </c>
       <c r="F73" s="19">
         <v>15000</v>
       </c>
       <c r="G73" s="20">
-        <v>14963.61</v>
+        <v>15178.56</v>
       </c>
       <c r="H73" s="21">
-        <v>5.1362108978999996E-3</v>
+        <v>4.8550208255999996E-3</v>
       </c>
       <c r="I73" s="20">
-        <v>7.63</v>
+        <v>6.63</v>
       </c>
       <c r="J73" s="15" t="s">
         <v>13</v>
@@ -3580,28 +3707,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="16" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D74" s="18">
-        <v>7.35</v>
+        <v>7.44</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F74" s="19">
         <v>15000</v>
       </c>
       <c r="G74" s="20">
-        <v>14954.93</v>
+        <v>15117.35</v>
       </c>
       <c r="H74" s="21">
-        <v>5.1332315159000001E-3</v>
+        <v>4.8354421683000004E-3</v>
       </c>
       <c r="I74" s="20">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="J74" s="15" t="s">
         <v>13</v>
@@ -3609,28 +3736,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D75" s="18">
-        <v>7.13</v>
+        <v>7.6</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F75" s="19">
-        <v>1500</v>
+        <v>15000</v>
       </c>
       <c r="G75" s="20">
-        <v>14896.43</v>
+        <v>15099.68</v>
       </c>
       <c r="H75" s="21">
-        <v>5.1131515794999999E-3</v>
+        <v>4.8297902343999999E-3</v>
       </c>
       <c r="I75" s="20">
-        <v>7.62</v>
+        <v>6.54</v>
       </c>
       <c r="J75" s="15" t="s">
         <v>13</v>
@@ -3638,28 +3765,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D76" s="18">
-        <v>8</v>
+        <v>8.1577000000000002</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="F76" s="19">
-        <v>13700</v>
+        <v>15000</v>
       </c>
       <c r="G76" s="20">
-        <v>13548.48</v>
+        <v>15093.57</v>
       </c>
       <c r="H76" s="21">
-        <v>4.6504720870000002E-3</v>
+        <v>4.8278358871000002E-3</v>
       </c>
       <c r="I76" s="20">
-        <v>8.1199999999999992</v>
+        <v>7.11</v>
       </c>
       <c r="J76" s="15" t="s">
         <v>13</v>
@@ -3667,28 +3794,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="16" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D77" s="18">
-        <v>8.75</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F77" s="19">
-        <v>1300</v>
+        <v>15000</v>
       </c>
       <c r="G77" s="20">
-        <v>13456.82</v>
+        <v>15042.05</v>
       </c>
       <c r="H77" s="21">
-        <v>4.6190100875000001E-3</v>
+        <v>4.8113566773999999E-3</v>
       </c>
       <c r="I77" s="20">
-        <v>7.65</v>
+        <v>6.91</v>
       </c>
       <c r="J77" s="15" t="s">
         <v>13</v>
@@ -3696,57 +3823,57 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="16" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D78" s="18">
-        <v>5.83</v>
+        <v>7.68</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F78" s="19">
-        <v>1250</v>
+        <v>13500</v>
       </c>
       <c r="G78" s="20">
-        <v>12271.23</v>
+        <v>13796.68</v>
       </c>
       <c r="H78" s="21">
-        <v>4.2120601416999999E-3</v>
+        <v>4.4130120857000001E-3</v>
       </c>
       <c r="I78" s="20">
-        <v>6.21</v>
-      </c>
-      <c r="J78" s="15">
-        <v>8.3699999999999992</v>
+        <v>6.58</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="16" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D79" s="18">
-        <v>7.96</v>
+        <v>8.75</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F79" s="19">
-        <v>12000</v>
+        <v>1300</v>
       </c>
       <c r="G79" s="20">
-        <v>12066.01</v>
+        <v>13714.26</v>
       </c>
       <c r="H79" s="21">
-        <v>4.1416190381999996E-3</v>
+        <v>4.3866491885999996E-3</v>
       </c>
       <c r="I79" s="20">
-        <v>7.87</v>
+        <v>6.92</v>
       </c>
       <c r="J79" s="15" t="s">
         <v>13</v>
@@ -3754,28 +3881,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C80" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="D80" s="18">
+        <v>8</v>
+      </c>
+      <c r="E80" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D80" s="18">
-        <v>7.68</v>
-      </c>
-      <c r="E80" s="17" t="s">
-        <v>39</v>
-      </c>
       <c r="F80" s="19">
-        <v>12000</v>
+        <v>13700</v>
       </c>
       <c r="G80" s="20">
-        <v>12034.14</v>
+        <v>13646.79</v>
       </c>
       <c r="H80" s="21">
-        <v>4.1306797634000003E-3</v>
+        <v>4.3650682049000003E-3</v>
       </c>
       <c r="I80" s="20">
-        <v>7.39</v>
+        <v>7.25</v>
       </c>
       <c r="J80" s="15" t="s">
         <v>13</v>
@@ -3783,28 +3910,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>127</v>
       </c>
       <c r="D81" s="18">
-        <v>7.9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F81" s="19">
-        <v>1150</v>
+        <v>1250</v>
       </c>
       <c r="G81" s="20">
-        <v>11536.82</v>
+        <v>13228.25</v>
       </c>
       <c r="H81" s="21">
-        <v>3.9599762764999996E-3</v>
+        <v>4.2311938178999997E-3</v>
       </c>
       <c r="I81" s="20">
-        <v>7.72</v>
+        <v>6.92</v>
       </c>
       <c r="J81" s="15" t="s">
         <v>13</v>
@@ -3812,28 +3939,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C82" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C82" s="17" t="s">
-        <v>129</v>
-      </c>
       <c r="D82" s="18">
-        <v>8.15</v>
+        <v>7.49</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="F82" s="19">
-        <v>11000</v>
+        <v>12850</v>
       </c>
       <c r="G82" s="20">
-        <v>11024.2</v>
+        <v>12984.18</v>
       </c>
       <c r="H82" s="21">
-        <v>3.7840211138999999E-3</v>
+        <v>4.1531254810999998E-3</v>
       </c>
       <c r="I82" s="20">
-        <v>7.89</v>
+        <v>6.63</v>
       </c>
       <c r="J82" s="15" t="s">
         <v>13</v>
@@ -3841,28 +3968,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="16" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D83" s="18">
-        <v>7.43</v>
+        <v>7.48</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F83" s="19">
-        <v>11000</v>
+        <v>12500</v>
       </c>
       <c r="G83" s="20">
-        <v>10959.51</v>
+        <v>12819.71</v>
       </c>
       <c r="H83" s="21">
-        <v>3.7618164798999998E-3</v>
+        <v>4.1005180352000001E-3</v>
       </c>
       <c r="I83" s="20">
-        <v>7.64</v>
+        <v>6.6</v>
       </c>
       <c r="J83" s="15" t="s">
         <v>13</v>
@@ -3870,28 +3997,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="16" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="C84" s="17" t="s">
         <v>131</v>
       </c>
       <c r="D84" s="18">
-        <v>7.69</v>
+        <v>7.4</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="F84" s="19">
-        <v>10500</v>
+        <v>12500</v>
       </c>
       <c r="G84" s="20">
-        <v>10627</v>
+        <v>12481.18</v>
       </c>
       <c r="H84" s="21">
-        <v>3.6476834942999999E-3</v>
+        <v>3.9922356815999998E-3</v>
       </c>
       <c r="I84" s="20">
-        <v>7.5</v>
+        <v>7.46</v>
       </c>
       <c r="J84" s="15" t="s">
         <v>13</v>
@@ -3899,57 +4026,57 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="16" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="C85" s="17" t="s">
         <v>133</v>
       </c>
       <c r="D85" s="18">
-        <v>7.84</v>
+        <v>5.83</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F85" s="19">
-        <v>100</v>
+        <v>1250</v>
       </c>
       <c r="G85" s="20">
-        <v>10172.049999999999</v>
+        <v>12437.56</v>
       </c>
       <c r="H85" s="21">
-        <v>3.4915233733000001E-3</v>
+        <v>3.9782833694000002E-3</v>
       </c>
       <c r="I85" s="20">
-        <v>7.54</v>
-      </c>
-      <c r="J85" s="15" t="s">
-        <v>13</v>
+        <v>5.93</v>
+      </c>
+      <c r="J85" s="15">
+        <v>6.88</v>
       </c>
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="16" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C86" s="17" t="s">
         <v>134</v>
       </c>
       <c r="D86" s="18">
-        <v>8.19</v>
+        <v>7.96</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F86" s="19">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="G86" s="20">
-        <v>10092.030000000001</v>
+        <v>12226.58</v>
       </c>
       <c r="H86" s="21">
-        <v>3.4640567661999998E-3</v>
+        <v>3.9107992144999998E-3</v>
       </c>
       <c r="I86" s="20">
-        <v>7.86</v>
+        <v>6.84</v>
       </c>
       <c r="J86" s="15" t="s">
         <v>13</v>
@@ -3963,22 +4090,22 @@
         <v>136</v>
       </c>
       <c r="D87" s="18">
-        <v>8.1999999999999993</v>
+        <v>7.68</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F87" s="19">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="G87" s="20">
-        <v>10049.61</v>
+        <v>12127.48</v>
       </c>
       <c r="H87" s="21">
-        <v>3.4494962380000002E-3</v>
+        <v>3.8791010453000001E-3</v>
       </c>
       <c r="I87" s="20">
-        <v>7.92</v>
+        <v>6.48</v>
       </c>
       <c r="J87" s="15" t="s">
         <v>13</v>
@@ -3986,28 +4113,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="16" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C88" s="17" t="s">
         <v>137</v>
       </c>
       <c r="D88" s="18">
-        <v>7.83</v>
+        <v>7.9</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F88" s="19">
-        <v>10000</v>
+        <v>1150</v>
       </c>
       <c r="G88" s="20">
-        <v>10035.290000000001</v>
+        <v>11736.28</v>
       </c>
       <c r="H88" s="21">
-        <v>3.4445809441E-3</v>
+        <v>3.7539716424999999E-3</v>
       </c>
       <c r="I88" s="20">
-        <v>7.61</v>
+        <v>6.79</v>
       </c>
       <c r="J88" s="15" t="s">
         <v>13</v>
@@ -4015,28 +4142,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="16" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>138</v>
       </c>
       <c r="D89" s="18">
-        <v>7.65</v>
+        <v>7.79</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F89" s="19">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G89" s="20">
-        <v>10025.700000000001</v>
+        <v>11237.62</v>
       </c>
       <c r="H89" s="21">
-        <v>3.4412892075E-3</v>
+        <v>3.5944700373000001E-3</v>
       </c>
       <c r="I89" s="20">
-        <v>7.59</v>
+        <v>6.57</v>
       </c>
       <c r="J89" s="15" t="s">
         <v>13</v>
@@ -4044,28 +4171,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="16" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D90" s="18">
-        <v>7.77</v>
+        <v>8.15</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="F90" s="19">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G90" s="20">
-        <v>10022.790000000001</v>
+        <v>11069.11</v>
       </c>
       <c r="H90" s="21">
-        <v>3.4402903594000001E-3</v>
+        <v>3.5405703551999999E-3</v>
       </c>
       <c r="I90" s="20">
-        <v>7.62</v>
+        <v>6.94</v>
       </c>
       <c r="J90" s="15" t="s">
         <v>13</v>
@@ -4073,28 +4200,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D91" s="18">
-        <v>7.83</v>
+        <v>7.69</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F91" s="19">
-        <v>1000</v>
+        <v>10500</v>
       </c>
       <c r="G91" s="20">
-        <v>10004.629999999999</v>
+        <v>10858.49</v>
       </c>
       <c r="H91" s="21">
-        <v>3.4340569979999999E-3</v>
+        <v>3.4732013501000002E-3</v>
       </c>
       <c r="I91" s="20">
-        <v>7.76</v>
+        <v>7.14</v>
       </c>
       <c r="J91" s="15" t="s">
         <v>13</v>
@@ -4102,28 +4229,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="16" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D92" s="18">
-        <v>7.7120000000000006</v>
+        <v>7.84</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F92" s="19">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G92" s="20">
-        <v>9995.07</v>
+        <v>10438.76</v>
       </c>
       <c r="H92" s="21">
-        <v>3.4307755587999998E-3</v>
+        <v>3.3389463291E-3</v>
       </c>
       <c r="I92" s="20">
-        <v>7.73</v>
+        <v>7.06</v>
       </c>
       <c r="J92" s="15" t="s">
         <v>13</v>
@@ -4131,28 +4258,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D93" s="18">
-        <v>8.2900000000000009</v>
+        <v>7.83</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="F93" s="19">
         <v>10000</v>
       </c>
       <c r="G93" s="20">
-        <v>9992.1299999999992</v>
+        <v>10367.42</v>
       </c>
       <c r="H93" s="21">
-        <v>3.4297664133E-3</v>
+        <v>3.3161274856000002E-3</v>
       </c>
       <c r="I93" s="20">
-        <v>8.3699999999999992</v>
+        <v>6.59</v>
       </c>
       <c r="J93" s="15" t="s">
         <v>13</v>
@@ -4160,28 +4287,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="16" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D94" s="18">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F94" s="19">
         <v>10000</v>
       </c>
       <c r="G94" s="20">
-        <v>9991.5300000000007</v>
+        <v>10280.82</v>
       </c>
       <c r="H94" s="21">
-        <v>3.4295604651999999E-3</v>
+        <v>3.2884275718000002E-3</v>
       </c>
       <c r="I94" s="20">
-        <v>7.9</v>
+        <v>7.11</v>
       </c>
       <c r="J94" s="15" t="s">
         <v>13</v>
@@ -4189,28 +4316,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="16" t="s">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="C95" s="17" t="s">
         <v>146</v>
       </c>
       <c r="D95" s="18">
-        <v>8.14</v>
+        <v>7.65</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F95" s="19">
         <v>10000</v>
       </c>
       <c r="G95" s="20">
-        <v>9988.24</v>
+        <v>10250.469999999999</v>
       </c>
       <c r="H95" s="21">
-        <v>3.4284311833000002E-3</v>
+        <v>3.2787198074999998E-3</v>
       </c>
       <c r="I95" s="20">
-        <v>8.42</v>
+        <v>7.13</v>
       </c>
       <c r="J95" s="15" t="s">
         <v>13</v>
@@ -4218,28 +4345,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="16" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C96" s="17" t="s">
         <v>147</v>
       </c>
       <c r="D96" s="18">
-        <v>7.44</v>
+        <v>8.19</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F96" s="19">
         <v>10000</v>
       </c>
       <c r="G96" s="20">
-        <v>9982.32</v>
+        <v>10205.01</v>
       </c>
       <c r="H96" s="21">
-        <v>3.4263991623999998E-3</v>
+        <v>3.2641789520999999E-3</v>
       </c>
       <c r="I96" s="20">
-        <v>7.7</v>
+        <v>6.85</v>
       </c>
       <c r="J96" s="15" t="s">
         <v>13</v>
@@ -4247,28 +4374,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C97" s="17" t="s">
-        <v>149</v>
-      </c>
       <c r="D97" s="18">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F97" s="19">
         <v>10000</v>
       </c>
       <c r="G97" s="20">
-        <v>9981.77</v>
+        <v>10169.299999999999</v>
       </c>
       <c r="H97" s="21">
-        <v>3.4262103767E-3</v>
+        <v>3.2527567359000001E-3</v>
       </c>
       <c r="I97" s="20">
-        <v>7.95</v>
+        <v>6.63</v>
       </c>
       <c r="J97" s="15" t="s">
         <v>13</v>
@@ -4276,28 +4403,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="16" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>150</v>
       </c>
       <c r="D98" s="18">
-        <v>7.54</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F98" s="19">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G98" s="20">
-        <v>9978.93</v>
+        <v>10162.77</v>
       </c>
       <c r="H98" s="21">
-        <v>3.4252355558000002E-3</v>
+        <v>3.2506680472999998E-3</v>
       </c>
       <c r="I98" s="20">
-        <v>7.77</v>
+        <v>7.14</v>
       </c>
       <c r="J98" s="15" t="s">
         <v>13</v>
@@ -4305,28 +4432,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C99" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C99" s="17" t="s">
-        <v>152</v>
-      </c>
       <c r="D99" s="18">
-        <v>7.38</v>
+        <v>7.7120000000000006</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F99" s="19">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G99" s="20">
-        <v>9957.77</v>
+        <v>10139.209999999999</v>
       </c>
       <c r="H99" s="21">
-        <v>3.4179724539999999E-3</v>
+        <v>3.2431321353999999E-3</v>
       </c>
       <c r="I99" s="20">
-        <v>7.92</v>
+        <v>7.09</v>
       </c>
       <c r="J99" s="15" t="s">
         <v>13</v>
@@ -4334,28 +4461,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="16" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D100" s="18">
-        <v>8.2799999999999994</v>
+        <v>7.77</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F100" s="19">
-        <v>8500</v>
+        <v>10000</v>
       </c>
       <c r="G100" s="20">
-        <v>8524.4</v>
+        <v>10128.76</v>
       </c>
       <c r="H100" s="21">
-        <v>2.9259728219000001E-3</v>
+        <v>3.2397895937999999E-3</v>
       </c>
       <c r="I100" s="20">
-        <v>8.01</v>
+        <v>6.55</v>
       </c>
       <c r="J100" s="15" t="s">
         <v>13</v>
@@ -4363,28 +4490,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="16" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D101" s="18">
-        <v>7.9613000000000005</v>
+        <v>7.83</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F101" s="19">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="G101" s="20">
-        <v>8018.5</v>
+        <v>10117.74</v>
       </c>
       <c r="H101" s="21">
-        <v>2.7523242777000002E-3</v>
+        <v>3.2362647317999999E-3</v>
       </c>
       <c r="I101" s="20">
-        <v>7.8</v>
+        <v>6.82</v>
       </c>
       <c r="J101" s="15" t="s">
         <v>13</v>
@@ -4392,28 +4519,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="16" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D102" s="18">
-        <v>7.86</v>
+        <v>7.54</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F102" s="19">
-        <v>78</v>
+        <v>1000</v>
       </c>
       <c r="G102" s="20">
-        <v>7945.2</v>
+        <v>10051.34</v>
       </c>
       <c r="H102" s="21">
-        <v>2.7271642889000001E-3</v>
+        <v>3.2150259988E-3</v>
       </c>
       <c r="I102" s="20">
-        <v>7.53</v>
+        <v>6.6</v>
       </c>
       <c r="J102" s="15" t="s">
         <v>13</v>
@@ -4421,28 +4548,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="16" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D103" s="18">
-        <v>8.0250000000000004</v>
+        <v>7.47</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F103" s="19">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="G103" s="20">
-        <v>7712.8</v>
+        <v>10029.01</v>
       </c>
       <c r="H103" s="21">
-        <v>2.6473937381E-3</v>
+        <v>3.2078835153000001E-3</v>
       </c>
       <c r="I103" s="20">
-        <v>7.54</v>
+        <v>6.73</v>
       </c>
       <c r="J103" s="15" t="s">
         <v>13</v>
@@ -4450,57 +4577,57 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="16" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D104" s="18">
-        <v>7.42</v>
+        <v>7.97</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F104" s="19">
-        <v>75</v>
+        <v>9500</v>
       </c>
       <c r="G104" s="20">
-        <v>7548.2</v>
+        <v>10015.86</v>
       </c>
       <c r="H104" s="21">
-        <v>2.5908953187000002E-3</v>
+        <v>3.2036773504999999E-3</v>
       </c>
       <c r="I104" s="20">
-        <v>7.34</v>
-      </c>
-      <c r="J104" s="15">
-        <v>7.32</v>
+        <v>7.03</v>
+      </c>
+      <c r="J104" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="16" t="s">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D105" s="18">
-        <v>7.95</v>
+        <v>7.19</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F105" s="19">
-        <v>750</v>
+        <v>10000</v>
       </c>
       <c r="G105" s="20">
-        <v>7532.34</v>
+        <v>9998.5</v>
       </c>
       <c r="H105" s="21">
-        <v>2.5854514248000002E-3</v>
+        <v>3.1981245733999999E-3</v>
       </c>
       <c r="I105" s="20">
-        <v>7.71</v>
+        <v>7.21</v>
       </c>
       <c r="J105" s="15" t="s">
         <v>13</v>
@@ -4508,28 +4635,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D106" s="18">
-        <v>8.3000000000000007</v>
+        <v>7.48</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="F106" s="19">
-        <v>750</v>
+        <v>10000</v>
       </c>
       <c r="G106" s="20">
-        <v>7503.98</v>
+        <v>9920.76</v>
       </c>
       <c r="H106" s="21">
-        <v>2.5757169461999999E-3</v>
+        <v>3.1732586230000001E-3</v>
       </c>
       <c r="I106" s="20">
-        <v>7.88</v>
+        <v>7.82</v>
       </c>
       <c r="J106" s="15" t="s">
         <v>13</v>
@@ -4537,28 +4664,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="16" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D107" s="18">
-        <v>8.07</v>
+        <v>6.23</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="F107" s="19">
-        <v>7500</v>
+        <v>900</v>
       </c>
       <c r="G107" s="20">
-        <v>7489.85</v>
+        <v>8953.75</v>
       </c>
       <c r="H107" s="21">
-        <v>2.5708668691999999E-3</v>
+        <v>2.8639503824000002E-3</v>
       </c>
       <c r="I107" s="20">
-        <v>8.1</v>
+        <v>6.59</v>
       </c>
       <c r="J107" s="15" t="s">
         <v>13</v>
@@ -4566,28 +4693,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="16" t="s">
-        <v>42</v>
+        <v>161</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D108" s="18">
-        <v>6.01</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F108" s="19">
-        <v>650</v>
+        <v>8500</v>
       </c>
       <c r="G108" s="20">
-        <v>6362.3</v>
+        <v>8589.1299999999992</v>
       </c>
       <c r="H108" s="21">
-        <v>2.1838389664E-3</v>
+        <v>2.7473228700999998E-3</v>
       </c>
       <c r="I108" s="20">
-        <v>7.76</v>
+        <v>7.28</v>
       </c>
       <c r="J108" s="15" t="s">
         <v>13</v>
@@ -4595,28 +4722,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="16" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D109" s="18">
-        <v>7.49</v>
+        <v>7.75</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F109" s="19">
-        <v>5650</v>
+        <v>8000</v>
       </c>
       <c r="G109" s="20">
-        <v>5636.16</v>
+        <v>8173.37</v>
       </c>
       <c r="H109" s="21">
-        <v>1.9345937520000001E-3</v>
+        <v>2.6143376951000001E-3</v>
       </c>
       <c r="I109" s="20">
-        <v>7.61</v>
+        <v>6.57</v>
       </c>
       <c r="J109" s="15" t="s">
         <v>13</v>
@@ -4624,28 +4751,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="16" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D110" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.86</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F110" s="19">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="G110" s="20">
-        <v>5116.18</v>
+        <v>8149.72</v>
       </c>
       <c r="H110" s="21">
-        <v>1.7561122932000001E-3</v>
+        <v>2.6067729957000001E-3</v>
       </c>
       <c r="I110" s="20">
-        <v>9.4700000000000006</v>
+        <v>7.06</v>
       </c>
       <c r="J110" s="15" t="s">
         <v>13</v>
@@ -4653,28 +4780,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="16" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D111" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.9613000000000005</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F111" s="19">
-        <v>481</v>
+        <v>8000</v>
       </c>
       <c r="G111" s="20">
-        <v>5110.4799999999996</v>
+        <v>8077.05</v>
       </c>
       <c r="H111" s="21">
-        <v>1.7541557865E-3</v>
+        <v>2.5835287378000002E-3</v>
       </c>
       <c r="I111" s="20">
-        <v>9.43</v>
+        <v>6.85</v>
       </c>
       <c r="J111" s="15" t="s">
         <v>13</v>
@@ -4682,28 +4809,28 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="16" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D112" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.0250000000000004</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F112" s="19">
-        <v>481</v>
+        <v>750</v>
       </c>
       <c r="G112" s="20">
-        <v>5079.71</v>
+        <v>7888.41</v>
       </c>
       <c r="H112" s="21">
-        <v>1.7435940832000001E-3</v>
+        <v>2.5231902650999999E-3</v>
       </c>
       <c r="I112" s="20">
-        <v>9.2799999999999994</v>
+        <v>7.13</v>
       </c>
       <c r="J112" s="15" t="s">
         <v>13</v>
@@ -4711,57 +4838,57 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="16" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D113" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.42</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F113" s="19">
-        <v>481</v>
+        <v>75</v>
       </c>
       <c r="G113" s="20">
-        <v>5074.25</v>
+        <v>7712.26</v>
       </c>
       <c r="H113" s="21">
-        <v>1.7417199558E-3</v>
+        <v>2.4668468491999998E-3</v>
       </c>
       <c r="I113" s="20">
-        <v>9.36</v>
-      </c>
-      <c r="J113" s="15" t="s">
-        <v>13</v>
+        <v>7.09</v>
+      </c>
+      <c r="J113" s="15">
+        <v>6.99</v>
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="16" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D114" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.42</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F114" s="19">
-        <v>481</v>
+        <v>7500</v>
       </c>
       <c r="G114" s="20">
-        <v>5061.13</v>
+        <v>7684.43</v>
       </c>
       <c r="H114" s="21">
-        <v>1.7372165581E-3</v>
+        <v>2.4579451333E-3</v>
       </c>
       <c r="I114" s="20">
-        <v>9.4499999999999993</v>
+        <v>6.65</v>
       </c>
       <c r="J114" s="15" t="s">
         <v>13</v>
@@ -4769,28 +4896,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="16" t="s">
-        <v>172</v>
+        <v>40</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D115" s="18">
-        <v>7.51</v>
+        <v>7.95</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F115" s="19">
-        <v>5000</v>
+        <v>750</v>
       </c>
       <c r="G115" s="20">
-        <v>5055.95</v>
+        <v>7634.35</v>
       </c>
       <c r="H115" s="21">
-        <v>1.7354385398E-3</v>
+        <v>2.4419265225999998E-3</v>
       </c>
       <c r="I115" s="20">
-        <v>7.47</v>
+        <v>6.85</v>
       </c>
       <c r="J115" s="15" t="s">
         <v>13</v>
@@ -4798,28 +4925,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="16" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D116" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.07</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="F116" s="19">
-        <v>481</v>
+        <v>7500</v>
       </c>
       <c r="G116" s="20">
-        <v>5043.3</v>
+        <v>7607.6</v>
       </c>
       <c r="H116" s="21">
-        <v>1.7310964681000001E-3</v>
+        <v>2.4333702560000001E-3</v>
       </c>
       <c r="I116" s="20">
-        <v>9.3000000000000007</v>
+        <v>7.34</v>
       </c>
       <c r="J116" s="15" t="s">
         <v>13</v>
@@ -4827,28 +4954,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B117" s="16" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D117" s="18">
-        <v>7.95</v>
+        <v>7.22</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F117" s="19">
-        <v>500</v>
+        <v>7500</v>
       </c>
       <c r="G117" s="20">
-        <v>5040.6000000000004</v>
+        <v>7529.3</v>
       </c>
       <c r="H117" s="21">
-        <v>1.7301697018E-3</v>
+        <v>2.4083251838000002E-3</v>
       </c>
       <c r="I117" s="20">
-        <v>7.51</v>
+        <v>7.26</v>
       </c>
       <c r="J117" s="15" t="s">
         <v>13</v>
@@ -4856,28 +4983,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="16" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D118" s="18">
-        <v>9.5399999999999991</v>
+        <v>6.01</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F118" s="19">
-        <v>481</v>
+        <v>650</v>
       </c>
       <c r="G118" s="20">
-        <v>5022.8599999999997</v>
+        <v>6452.38</v>
       </c>
       <c r="H118" s="21">
-        <v>1.724080504E-3</v>
+        <v>2.0638610825999999E-3</v>
       </c>
       <c r="I118" s="20">
-        <v>9.24</v>
+        <v>6.81</v>
       </c>
       <c r="J118" s="15" t="s">
         <v>13</v>
@@ -4885,28 +5012,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="16" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D119" s="18">
-        <v>7.7</v>
+        <v>7.51</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="F119" s="19">
         <v>5000</v>
       </c>
       <c r="G119" s="20">
-        <v>5017.88</v>
+        <v>5173.4399999999996</v>
       </c>
       <c r="H119" s="21">
-        <v>1.722371135E-3</v>
+        <v>1.6547787761E-3</v>
       </c>
       <c r="I119" s="20">
-        <v>7.52</v>
+        <v>7.1</v>
       </c>
       <c r="J119" s="15" t="s">
         <v>13</v>
@@ -4914,28 +5041,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D120" s="18">
-        <v>7.71</v>
+        <v>7.46</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F120" s="19">
         <v>5000</v>
       </c>
       <c r="G120" s="20">
-        <v>5017.8500000000004</v>
+        <v>5122.67</v>
       </c>
       <c r="H120" s="21">
-        <v>1.7223608376E-3</v>
+        <v>1.6385394616999999E-3</v>
       </c>
       <c r="I120" s="20">
-        <v>7.51</v>
+        <v>6.55</v>
       </c>
       <c r="J120" s="15" t="s">
         <v>13</v>
@@ -4943,28 +5070,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="16" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C121" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D121" s="18">
-        <v>7.54</v>
+        <v>9.58</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F121" s="19">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="G121" s="20">
-        <v>5005.0200000000004</v>
+        <v>5120.33</v>
       </c>
       <c r="H121" s="21">
-        <v>1.7179569815000001E-3</v>
+        <v>1.6377909883000001E-3</v>
       </c>
       <c r="I121" s="20">
-        <v>7.43</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="J121" s="15" t="s">
         <v>13</v>
@@ -4972,28 +5099,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="16" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="C122" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D122" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.95</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F122" s="19">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="G122" s="20">
-        <v>5000.5600000000004</v>
+        <v>5115.25</v>
       </c>
       <c r="H122" s="21">
-        <v>1.7164261009E-3</v>
+        <v>1.6361660973E-3</v>
       </c>
       <c r="I122" s="20">
-        <v>9.18</v>
+        <v>6.52</v>
       </c>
       <c r="J122" s="15" t="s">
         <v>13</v>
@@ -5001,28 +5128,28 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="16" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
       <c r="C123" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D123" s="18">
-        <v>7.8815</v>
+        <v>7.7</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F123" s="19">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G123" s="20">
-        <v>4998.8100000000004</v>
+        <v>5113.84</v>
       </c>
       <c r="H123" s="21">
-        <v>1.7158254190000001E-3</v>
+        <v>1.6357150941E-3</v>
       </c>
       <c r="I123" s="20">
-        <v>7.84</v>
+        <v>6.59</v>
       </c>
       <c r="J123" s="15" t="s">
         <v>13</v>
@@ -5030,28 +5157,28 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="16" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C124" s="17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D124" s="18">
-        <v>7.82</v>
+        <v>7.59</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F124" s="19">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G124" s="20">
-        <v>4998</v>
+        <v>5097.22</v>
       </c>
       <c r="H124" s="21">
-        <v>1.7155473891E-3</v>
+        <v>1.6303990136000001E-3</v>
       </c>
       <c r="I124" s="20">
-        <v>7.84</v>
+        <v>6.52</v>
       </c>
       <c r="J124" s="15" t="s">
         <v>13</v>
@@ -5059,28 +5186,28 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="16" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="C125" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D125" s="18">
-        <v>8.07</v>
+        <v>9.58</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F125" s="19">
-        <v>5000</v>
+        <v>481</v>
       </c>
       <c r="G125" s="20">
-        <v>4995.82</v>
+        <v>5095.5600000000004</v>
       </c>
       <c r="H125" s="21">
-        <v>1.7147991111E-3</v>
+        <v>1.6298680453000001E-3</v>
       </c>
       <c r="I125" s="20">
-        <v>8.7200000000000006</v>
+        <v>8.93</v>
       </c>
       <c r="J125" s="15" t="s">
         <v>13</v>
@@ -5088,28 +5215,28 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B126" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C126" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D126" s="18">
-        <v>7.55</v>
+        <v>7.71</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F126" s="19">
         <v>5000</v>
       </c>
       <c r="G126" s="20">
-        <v>4995.25</v>
+        <v>5092.7299999999996</v>
       </c>
       <c r="H126" s="21">
-        <v>1.7146034605E-3</v>
+        <v>1.6289628403E-3</v>
       </c>
       <c r="I126" s="20">
-        <v>7.62</v>
+        <v>6.52</v>
       </c>
       <c r="J126" s="15" t="s">
         <v>13</v>
@@ -5117,28 +5244,28 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="16" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D127" s="18">
-        <v>8</v>
+        <v>9.58</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F127" s="19">
-        <v>5000</v>
+        <v>481</v>
       </c>
       <c r="G127" s="20">
-        <v>4993.62</v>
+        <v>5087.43</v>
       </c>
       <c r="H127" s="21">
-        <v>1.7140439681999999E-3</v>
+        <v>1.6272675798999999E-3</v>
       </c>
       <c r="I127" s="20">
-        <v>7.95</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="J127" s="15" t="s">
         <v>13</v>
@@ -5146,28 +5273,28 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="16" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D128" s="18">
-        <v>7.46</v>
+        <v>9.58</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F128" s="19">
-        <v>5000</v>
+        <v>481</v>
       </c>
       <c r="G128" s="20">
-        <v>4991.21</v>
+        <v>5085.41</v>
       </c>
       <c r="H128" s="21">
-        <v>1.7132167434999999E-3</v>
+        <v>1.6266214619E-3</v>
       </c>
       <c r="I128" s="20">
-        <v>7.5</v>
+        <v>8.83</v>
       </c>
       <c r="J128" s="15" t="s">
         <v>13</v>
@@ -5175,28 +5302,28 @@
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="16" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="C129" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D129" s="18">
-        <v>7.51</v>
+        <v>9.58</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F129" s="19">
-        <v>5000</v>
+        <v>481</v>
       </c>
       <c r="G129" s="20">
-        <v>4990.09</v>
+        <v>5080.25</v>
       </c>
       <c r="H129" s="21">
-        <v>1.7128323071E-3</v>
+        <v>1.6249709820000001E-3</v>
       </c>
       <c r="I129" s="20">
-        <v>7.61</v>
+        <v>8.81</v>
       </c>
       <c r="J129" s="15" t="s">
         <v>13</v>
@@ -5204,28 +5331,28 @@
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="16" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="C130" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D130" s="18">
-        <v>7.56</v>
+        <v>9.58</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F130" s="19">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="G130" s="20">
-        <v>4980.55</v>
+        <v>5061.38</v>
       </c>
       <c r="H130" s="21">
-        <v>1.7095577329E-3</v>
+        <v>1.6189352156E-3</v>
       </c>
       <c r="I130" s="20">
-        <v>7.72</v>
+        <v>8.25</v>
       </c>
       <c r="J130" s="15" t="s">
         <v>13</v>
@@ -5233,28 +5360,28 @@
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C131" s="17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D131" s="18">
-        <v>9.5399999999999991</v>
+        <v>9.58</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F131" s="19">
         <v>481</v>
       </c>
       <c r="G131" s="20">
-        <v>4976.2299999999996</v>
+        <v>5060.2</v>
       </c>
       <c r="H131" s="21">
-        <v>1.7080749068000001E-3</v>
+        <v>1.6185577803E-3</v>
       </c>
       <c r="I131" s="20">
-        <v>9.1199999999999992</v>
+        <v>7.06</v>
       </c>
       <c r="J131" s="15" t="s">
         <v>13</v>
@@ -5262,28 +5389,28 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="16" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C132" s="17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D132" s="18">
-        <v>9.5399999999999991</v>
+        <v>9.58</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F132" s="19">
         <v>481</v>
       </c>
       <c r="G132" s="20">
-        <v>4949.74</v>
+        <v>5059.8</v>
       </c>
       <c r="H132" s="21">
-        <v>1.6989822997E-3</v>
+        <v>1.6184298361E-3</v>
       </c>
       <c r="I132" s="20">
-        <v>9.0399999999999991</v>
+        <v>7.64</v>
       </c>
       <c r="J132" s="15" t="s">
         <v>13</v>
@@ -5291,28 +5418,28 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="16" t="s">
-        <v>191</v>
+        <v>112</v>
       </c>
       <c r="C133" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D133" s="18">
-        <v>5.81</v>
+        <v>9.58</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F133" s="19">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="G133" s="20">
-        <v>4916.8900000000003</v>
+        <v>5059.26</v>
       </c>
       <c r="H133" s="21">
-        <v>1.6877066431000001E-3</v>
+        <v>1.6182571114E-3</v>
       </c>
       <c r="I133" s="20">
-        <v>7.72</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="J133" s="15" t="s">
         <v>13</v>
@@ -5320,28 +5447,28 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="16" t="s">
-        <v>193</v>
+        <v>112</v>
       </c>
       <c r="C134" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D134" s="18">
-        <v>6.35</v>
+        <v>9.58</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F134" s="19">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="G134" s="20">
-        <v>4882.8599999999997</v>
+        <v>5053.84</v>
       </c>
       <c r="H134" s="21">
-        <v>1.6760259553E-3</v>
+        <v>1.6165234678999999E-3</v>
       </c>
       <c r="I134" s="20">
-        <v>7.92</v>
+        <v>8.01</v>
       </c>
       <c r="J134" s="15" t="s">
         <v>13</v>
@@ -5349,28 +5476,28 @@
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="16" t="s">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="C135" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D135" s="18">
-        <v>7.97</v>
+        <v>7.55</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F135" s="19">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="G135" s="20">
-        <v>4646.83</v>
+        <v>5053.18</v>
       </c>
       <c r="H135" s="21">
-        <v>1.5950094186E-3</v>
+        <v>1.61631236E-3</v>
       </c>
       <c r="I135" s="20">
-        <v>7.42</v>
+        <v>6.55</v>
       </c>
       <c r="J135" s="15" t="s">
         <v>13</v>
@@ -5378,28 +5505,28 @@
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="16" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
       <c r="C136" s="17" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D136" s="18">
-        <v>7.96</v>
+        <v>7.51</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F136" s="19">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="G136" s="20">
-        <v>4541.43</v>
+        <v>5050.54</v>
       </c>
       <c r="H136" s="21">
-        <v>1.5588312083E-3</v>
+        <v>1.6154679284000001E-3</v>
       </c>
       <c r="I136" s="20">
-        <v>7.82</v>
+        <v>6.55</v>
       </c>
       <c r="J136" s="15" t="s">
         <v>13</v>
@@ -5407,28 +5534,28 @@
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B137" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C137" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D137" s="18">
+        <v>7.54</v>
+      </c>
+      <c r="E137" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C137" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="D137" s="18">
-        <v>7.56</v>
-      </c>
-      <c r="E137" s="17" t="s">
-        <v>39</v>
-      </c>
       <c r="F137" s="19">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="G137" s="20">
-        <v>4004.6</v>
+        <v>5035.38</v>
       </c>
       <c r="H137" s="21">
-        <v>1.3745660412999999E-3</v>
+        <v>1.6106188441999999E-3</v>
       </c>
       <c r="I137" s="20">
-        <v>7.48</v>
+        <v>6.34</v>
       </c>
       <c r="J137" s="15" t="s">
         <v>13</v>
@@ -5436,28 +5563,28 @@
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B138" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C138" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D138" s="18">
+        <v>7.27</v>
+      </c>
+      <c r="E138" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C138" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="D138" s="18">
-        <v>7.8</v>
-      </c>
-      <c r="E138" s="17" t="s">
-        <v>39</v>
-      </c>
       <c r="F138" s="19">
-        <v>3750</v>
+        <v>5000</v>
       </c>
       <c r="G138" s="20">
-        <v>3755.63</v>
+        <v>5021.1000000000004</v>
       </c>
       <c r="H138" s="21">
-        <v>1.2891078913E-3</v>
+        <v>1.6060512371999999E-3</v>
       </c>
       <c r="I138" s="20">
-        <v>7.63</v>
+        <v>7.03</v>
       </c>
       <c r="J138" s="15" t="s">
         <v>13</v>
@@ -5465,28 +5592,28 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="16" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C139" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D139" s="18">
-        <v>7.95</v>
+        <v>7.21</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F139" s="19">
-        <v>350</v>
+        <v>5000</v>
       </c>
       <c r="G139" s="20">
-        <v>3512.86</v>
+        <v>5016.51</v>
       </c>
       <c r="H139" s="21">
-        <v>1.2057778714E-3</v>
+        <v>1.6045830778000001E-3</v>
       </c>
       <c r="I139" s="20">
-        <v>7.68</v>
+        <v>7.27</v>
       </c>
       <c r="J139" s="15" t="s">
         <v>13</v>
@@ -5494,28 +5621,28 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B140" s="16" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C140" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D140" s="18">
-        <v>7.63</v>
+        <v>8.1100000000000012</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F140" s="19">
-        <v>350</v>
+        <v>5000</v>
       </c>
       <c r="G140" s="20">
-        <v>3498.1</v>
+        <v>5000.93</v>
       </c>
       <c r="H140" s="21">
-        <v>1.2007115489999999E-3</v>
+        <v>1.5995996521999999E-3</v>
       </c>
       <c r="I140" s="20">
-        <v>7.62</v>
+        <v>7.36</v>
       </c>
       <c r="J140" s="15" t="s">
         <v>13</v>
@@ -5523,28 +5650,28 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="16" t="s">
-        <v>193</v>
+        <v>53</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D141" s="18">
-        <v>7.96</v>
+        <v>5.81</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F141" s="19">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="G141" s="20">
-        <v>3497.75</v>
+        <v>4975.83</v>
       </c>
       <c r="H141" s="21">
-        <v>1.2005914125999999E-3</v>
+        <v>1.5915711551999999E-3</v>
       </c>
       <c r="I141" s="20">
-        <v>7.92</v>
+        <v>6.51</v>
       </c>
       <c r="J141" s="15" t="s">
         <v>13</v>
@@ -5552,28 +5679,28 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B142" s="16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C142" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D142" s="18">
-        <v>7.38</v>
+        <v>7.96</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F142" s="19">
-        <v>350</v>
+        <v>4500</v>
       </c>
       <c r="G142" s="20">
-        <v>3487.18</v>
+        <v>4631.9399999999996</v>
       </c>
       <c r="H142" s="21">
-        <v>1.1969632942E-3</v>
+        <v>1.4815743498E-3</v>
       </c>
       <c r="I142" s="20">
-        <v>7.82</v>
+        <v>6.89</v>
       </c>
       <c r="J142" s="15" t="s">
         <v>13</v>
@@ -5581,28 +5708,28 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="16" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="C143" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D143" s="18">
-        <v>8.85</v>
+        <v>7.56</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="F143" s="19">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G143" s="20">
-        <v>3017.53</v>
+        <v>4081.88</v>
       </c>
       <c r="H143" s="21">
-        <v>1.0357574456E-3</v>
+        <v>1.3056319180999999E-3</v>
       </c>
       <c r="I143" s="20">
-        <v>8.6199999999999992</v>
+        <v>6.53</v>
       </c>
       <c r="J143" s="15" t="s">
         <v>13</v>
@@ -5610,28 +5737,28 @@
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B144" s="16" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="C144" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D144" s="18">
-        <v>7.96</v>
+        <v>7.8</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F144" s="19">
-        <v>3000</v>
+        <v>3750</v>
       </c>
       <c r="G144" s="20">
-        <v>3016.77</v>
+        <v>3793.54</v>
       </c>
       <c r="H144" s="21">
-        <v>1.035496578E-3</v>
+        <v>1.2134033599E-3</v>
       </c>
       <c r="I144" s="20">
-        <v>7.95</v>
+        <v>6.56</v>
       </c>
       <c r="J144" s="15" t="s">
         <v>13</v>
@@ -5639,28 +5766,28 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B145" s="16" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C145" s="17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D145" s="18">
-        <v>7.59</v>
+        <v>7.95</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F145" s="19">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G145" s="20">
-        <v>3007.28</v>
+        <v>3554.23</v>
       </c>
       <c r="H145" s="21">
-        <v>1.0322391661E-3</v>
+        <v>1.1368575588E-3</v>
       </c>
       <c r="I145" s="20">
-        <v>7.49</v>
+        <v>6.71</v>
       </c>
       <c r="J145" s="15" t="s">
         <v>13</v>
@@ -5668,28 +5795,28 @@
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B146" s="16" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C146" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D146" s="18">
-        <v>6.4</v>
+        <v>7.63</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F146" s="19">
-        <v>265</v>
+        <v>350</v>
       </c>
       <c r="G146" s="20">
-        <v>2590.0300000000002</v>
+        <v>3541.04</v>
       </c>
       <c r="H146" s="21">
-        <v>8.8901944860000004E-4</v>
+        <v>1.1326385997E-3</v>
       </c>
       <c r="I146" s="20">
-        <v>7.76</v>
+        <v>6.55</v>
       </c>
       <c r="J146" s="15" t="s">
         <v>13</v>
@@ -5697,28 +5824,28 @@
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B147" s="16" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="C147" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D147" s="18">
-        <v>8.48</v>
+        <v>7.96</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F147" s="19">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G147" s="20">
-        <v>2521.38</v>
+        <v>3509.98</v>
       </c>
       <c r="H147" s="21">
-        <v>8.6545555739999996E-4</v>
+        <v>1.1227037345E-3</v>
       </c>
       <c r="I147" s="20">
-        <v>7.76</v>
+        <v>7.02</v>
       </c>
       <c r="J147" s="15" t="s">
         <v>13</v>
@@ -5726,28 +5853,28 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" s="16" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="C148" s="17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D148" s="18">
-        <v>8.25</v>
+        <v>7.59</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="F148" s="19">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="G148" s="20">
-        <v>2512.84</v>
+        <v>3071.11</v>
       </c>
       <c r="H148" s="21">
-        <v>8.6252422990000001E-4</v>
+        <v>9.8232658480000004E-4</v>
       </c>
       <c r="I148" s="20">
-        <v>7.97</v>
+        <v>6.56</v>
       </c>
       <c r="J148" s="15" t="s">
         <v>13</v>
@@ -5755,28 +5882,28 @@
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B149" s="16" t="s">
-        <v>63</v>
+        <v>209</v>
       </c>
       <c r="C149" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D149" s="18">
-        <v>7.51</v>
+        <v>8.85</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="F149" s="19">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G149" s="20">
-        <v>2503.17</v>
+        <v>3062.18</v>
       </c>
       <c r="H149" s="21">
-        <v>8.5920503359999999E-4</v>
+        <v>9.7947023109999989E-4</v>
       </c>
       <c r="I149" s="20">
-        <v>7.47</v>
+        <v>7.98</v>
       </c>
       <c r="J149" s="15" t="s">
         <v>13</v>
@@ -5784,28 +5911,28 @@
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B150" s="16" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="C150" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D150" s="18">
-        <v>8.3000000000000007</v>
+        <v>7.96</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F150" s="19">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="G150" s="20">
-        <v>2502.8200000000002</v>
+        <v>3060.61</v>
       </c>
       <c r="H150" s="21">
-        <v>8.5908489720000003E-4</v>
+        <v>9.7896805019999996E-4</v>
       </c>
       <c r="I150" s="20">
-        <v>7.61</v>
+        <v>7.2</v>
       </c>
       <c r="J150" s="15" t="s">
         <v>13</v>
@@ -5813,28 +5940,28 @@
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="16" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="C151" s="17" t="s">
         <v>213</v>
       </c>
       <c r="D151" s="18">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F151" s="19">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="G151" s="20">
-        <v>2502.4299999999998</v>
+        <v>2636.14</v>
       </c>
       <c r="H151" s="21">
-        <v>8.5895103100000003E-4</v>
+        <v>8.431968908E-4</v>
       </c>
       <c r="I151" s="20">
-        <v>7.78</v>
+        <v>7</v>
       </c>
       <c r="J151" s="15" t="s">
         <v>13</v>
@@ -5842,28 +5969,28 @@
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B152" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C152" s="17" t="s">
         <v>214</v>
       </c>
       <c r="D152" s="18">
-        <v>7.7201000000000004</v>
+        <v>6.4</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F152" s="19">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="G152" s="20">
-        <v>2497.88</v>
+        <v>2633.24</v>
       </c>
       <c r="H152" s="21">
-        <v>8.5738925809999999E-4</v>
+        <v>8.4226929549999999E-4</v>
       </c>
       <c r="I152" s="20">
-        <v>7.8</v>
+        <v>6.82</v>
       </c>
       <c r="J152" s="15" t="s">
         <v>13</v>
@@ -5871,28 +5998,28 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B153" s="16" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="C153" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D153" s="18">
-        <v>7.82</v>
+        <v>8.25</v>
       </c>
       <c r="E153" s="17" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="F153" s="19">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="G153" s="20">
-        <v>2497.61</v>
+        <v>2548.33</v>
       </c>
       <c r="H153" s="21">
-        <v>8.5729658149999997E-4</v>
+        <v>8.1510994589999999E-4</v>
       </c>
       <c r="I153" s="20">
-        <v>7.84</v>
+        <v>7.2</v>
       </c>
       <c r="J153" s="15" t="s">
         <v>13</v>
@@ -5900,28 +6027,28 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B154" s="16" t="s">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="C154" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D154" s="18">
-        <v>7.8376000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="E154" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F154" s="19">
         <v>250</v>
       </c>
       <c r="G154" s="20">
-        <v>2495.35</v>
+        <v>2541.23</v>
       </c>
       <c r="H154" s="21">
-        <v>8.5652084379999997E-4</v>
+        <v>8.1283893679999996E-4</v>
       </c>
       <c r="I154" s="20">
-        <v>7.92</v>
+        <v>6.82</v>
       </c>
       <c r="J154" s="15" t="s">
         <v>13</v>
@@ -5929,28 +6056,28 @@
     </row>
     <row r="155" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B155" s="16" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C155" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D155" s="18">
-        <v>6.37</v>
+        <v>7.56</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F155" s="19">
         <v>250</v>
       </c>
       <c r="G155" s="20">
-        <v>2489.16</v>
+        <v>2535.27</v>
       </c>
       <c r="H155" s="21">
-        <v>8.543961463E-4</v>
+        <v>8.1093256859999998E-4</v>
       </c>
       <c r="I155" s="20">
-        <v>7.83</v>
+        <v>6.79</v>
       </c>
       <c r="J155" s="15" t="s">
         <v>13</v>
@@ -5958,28 +6085,28 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B156" s="16" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C156" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D156" s="18">
-        <v>6.4</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="E156" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F156" s="19">
         <v>250</v>
       </c>
       <c r="G156" s="20">
-        <v>2448.7199999999998</v>
+        <v>2531.1</v>
       </c>
       <c r="H156" s="21">
-        <v>8.4051524659999998E-4</v>
+        <v>8.0959875049999995E-4</v>
       </c>
       <c r="I156" s="20">
-        <v>7.73</v>
+        <v>6.55</v>
       </c>
       <c r="J156" s="15" t="s">
         <v>13</v>
@@ -5987,28 +6114,28 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B157" s="16" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C157" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D157" s="18">
-        <v>6.17</v>
+        <v>7.9</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F157" s="19">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="G157" s="20">
-        <v>2441.52</v>
+        <v>2528.8000000000002</v>
       </c>
       <c r="H157" s="21">
-        <v>8.3804386980000005E-4</v>
+        <v>8.0886307149999998E-4</v>
       </c>
       <c r="I157" s="20">
-        <v>7.76</v>
+        <v>6.85</v>
       </c>
       <c r="J157" s="15" t="s">
         <v>13</v>
@@ -6016,28 +6143,28 @@
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B158" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C158" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D158" s="18">
-        <v>8.25</v>
+        <v>7.4</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F158" s="19">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G158" s="20">
-        <v>2003.23</v>
+        <v>2510.15</v>
       </c>
       <c r="H158" s="21">
-        <v>6.8760224010000004E-4</v>
+        <v>8.0289767440000004E-4</v>
       </c>
       <c r="I158" s="20">
-        <v>7.84</v>
+        <v>6.6</v>
       </c>
       <c r="J158" s="15" t="s">
         <v>13</v>
@@ -6045,28 +6172,28 @@
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B159" s="16" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C159" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D159" s="18">
-        <v>7.2</v>
+        <v>7.82</v>
       </c>
       <c r="E159" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F159" s="19">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G159" s="20">
-        <v>1990.06</v>
+        <v>2509.64</v>
       </c>
       <c r="H159" s="21">
-        <v>6.8308168009999996E-4</v>
+        <v>8.0273454560000001E-4</v>
       </c>
       <c r="I159" s="20">
-        <v>7.8</v>
+        <v>6.75</v>
       </c>
       <c r="J159" s="15" t="s">
         <v>13</v>
@@ -6074,28 +6201,28 @@
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B160" s="16" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="C160" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D160" s="18">
-        <v>8.58</v>
+        <v>7.9</v>
       </c>
       <c r="E160" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F160" s="19">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G160" s="20">
-        <v>1503.05</v>
+        <v>2507.64</v>
       </c>
       <c r="H160" s="21">
-        <v>5.1591706740000004E-4</v>
+        <v>8.0209482469999996E-4</v>
       </c>
       <c r="I160" s="20">
-        <v>7.82</v>
+        <v>6.93</v>
       </c>
       <c r="J160" s="15" t="s">
         <v>13</v>
@@ -6103,28 +6230,28 @@
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B161" s="16" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D161" s="18">
-        <v>8.0299999999999994</v>
+        <v>7.19</v>
       </c>
       <c r="E161" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F161" s="19">
-        <v>125</v>
+        <v>2500</v>
       </c>
       <c r="G161" s="20">
-        <v>1254.9100000000001</v>
+        <v>2507.25</v>
       </c>
       <c r="H161" s="21">
-        <v>4.3074381229999997E-4</v>
+        <v>8.0197007910000004E-4</v>
       </c>
       <c r="I161" s="20">
-        <v>7.64</v>
+        <v>7.08</v>
       </c>
       <c r="J161" s="15" t="s">
         <v>13</v>
@@ -6132,28 +6259,28 @@
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B162" s="16" t="s">
-        <v>47</v>
+        <v>227</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D162" s="18">
-        <v>8.11</v>
+        <v>7.8376000000000001</v>
       </c>
       <c r="E162" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F162" s="19">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="G162" s="20">
-        <v>1251.8599999999999</v>
+        <v>2502.52</v>
       </c>
       <c r="H162" s="21">
-        <v>4.296969096E-4</v>
+        <v>8.004571393E-4</v>
       </c>
       <c r="I162" s="20">
-        <v>7.72</v>
+        <v>6.65</v>
       </c>
       <c r="J162" s="15" t="s">
         <v>13</v>
@@ -6161,28 +6288,28 @@
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B163" s="16" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C163" s="17" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D163" s="18">
-        <v>7.7249999999999996</v>
+        <v>8</v>
       </c>
       <c r="E163" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F163" s="19">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="G163" s="20">
-        <v>1010.25</v>
+        <v>2500.64</v>
       </c>
       <c r="H163" s="21">
-        <v>3.4676505600000001E-4</v>
+        <v>7.9985580159999995E-4</v>
       </c>
       <c r="I163" s="20">
-        <v>7.34</v>
+        <v>7.1</v>
       </c>
       <c r="J163" s="15" t="s">
         <v>13</v>
@@ -6190,28 +6317,28 @@
     </row>
     <row r="164" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B164" s="16" t="s">
-        <v>227</v>
+        <v>70</v>
       </c>
       <c r="C164" s="17" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D164" s="18">
-        <v>7.63</v>
+        <v>6.4</v>
       </c>
       <c r="E164" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F164" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G164" s="20">
-        <v>1006.13</v>
+        <v>2490.46</v>
       </c>
       <c r="H164" s="21">
-        <v>3.4535087919999999E-4</v>
+        <v>7.9659962239999997E-4</v>
       </c>
       <c r="I164" s="20">
-        <v>7.37</v>
+        <v>6.67</v>
       </c>
       <c r="J164" s="15" t="s">
         <v>13</v>
@@ -6219,28 +6346,28 @@
     </row>
     <row r="165" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B165" s="16" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C165" s="17" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D165" s="18">
-        <v>7.77</v>
+        <v>6.17</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F165" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G165" s="20">
-        <v>999.83</v>
+        <v>2480.0500000000002</v>
       </c>
       <c r="H165" s="21">
-        <v>3.4318842450000001E-4</v>
+        <v>7.932698753E-4</v>
       </c>
       <c r="I165" s="20">
-        <v>7.75</v>
+        <v>6.82</v>
       </c>
       <c r="J165" s="15" t="s">
         <v>13</v>
@@ -6248,28 +6375,28 @@
     </row>
     <row r="166" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B166" s="16" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="C166" s="17" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D166" s="18">
-        <v>7.54</v>
+        <v>6.35</v>
       </c>
       <c r="E166" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F166" s="19">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G166" s="20">
-        <v>999.02</v>
+        <v>2472.54</v>
       </c>
       <c r="H166" s="21">
-        <v>3.4291039469999999E-4</v>
+        <v>7.9086772339999995E-4</v>
       </c>
       <c r="I166" s="20">
-        <v>7.59</v>
+        <v>7.24</v>
       </c>
       <c r="J166" s="15" t="s">
         <v>13</v>
@@ -6277,28 +6404,28 @@
     </row>
     <row r="167" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B167" s="16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C167" s="17" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D167" s="18">
-        <v>7.15</v>
+        <v>7.66</v>
       </c>
       <c r="E167" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F167" s="19">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="G167" s="20">
-        <v>995.11</v>
+        <v>2055.35</v>
       </c>
       <c r="H167" s="21">
-        <v>3.4156829979999998E-4</v>
+        <v>6.5742514789999997E-4</v>
       </c>
       <c r="I167" s="20">
-        <v>7.78</v>
+        <v>6.92</v>
       </c>
       <c r="J167" s="15" t="s">
         <v>13</v>
@@ -6306,28 +6433,28 @@
     </row>
     <row r="168" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B168" s="16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C168" s="17" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D168" s="18">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F168" s="19">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="G168" s="20">
-        <v>634.4</v>
+        <v>2009.02</v>
       </c>
       <c r="H168" s="21">
-        <v>2.17755755E-4</v>
+        <v>6.4260601389999996E-4</v>
       </c>
       <c r="I168" s="20">
-        <v>7.52</v>
+        <v>6.74</v>
       </c>
       <c r="J168" s="15" t="s">
         <v>13</v>
@@ -6335,28 +6462,28 @@
     </row>
     <row r="169" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B169" s="16" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C169" s="17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D169" s="18">
         <v>7.68</v>
       </c>
       <c r="E169" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F169" s="19">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G169" s="20">
-        <v>505.58</v>
+        <v>1534.19</v>
       </c>
       <c r="H169" s="21">
-        <v>1.735387052E-4</v>
+        <v>4.9072668290000003E-4</v>
       </c>
       <c r="I169" s="20">
-        <v>7.5</v>
+        <v>6.58</v>
       </c>
       <c r="J169" s="15" t="s">
         <v>13</v>
@@ -6364,28 +6491,28 @@
     </row>
     <row r="170" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B170" s="16" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C170" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D170" s="18">
-        <v>7.7</v>
+        <v>7.79</v>
       </c>
       <c r="E170" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F170" s="19">
-        <v>50</v>
+        <v>1500</v>
       </c>
       <c r="G170" s="20">
-        <v>498.92</v>
+        <v>1531.41</v>
       </c>
       <c r="H170" s="21">
-        <v>1.7125268169999999E-4</v>
+        <v>4.898374709E-4</v>
       </c>
       <c r="I170" s="20">
-        <v>7.87</v>
+        <v>6.57</v>
       </c>
       <c r="J170" s="15" t="s">
         <v>13</v>
@@ -6393,28 +6520,28 @@
     </row>
     <row r="171" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B171" s="16" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C171" s="17" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D171" s="18">
-        <v>6.79</v>
+        <v>8.58</v>
       </c>
       <c r="E171" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F171" s="19">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G171" s="20">
-        <v>78.2</v>
-      </c>
-      <c r="H171" s="22" t="s">
-        <v>236</v>
+        <v>1504.47</v>
+      </c>
+      <c r="H171" s="21">
+        <v>4.812204307E-4</v>
       </c>
       <c r="I171" s="20">
-        <v>7.36</v>
+        <v>6.33</v>
       </c>
       <c r="J171" s="15" t="s">
         <v>13</v>
@@ -6422,28 +6549,28 @@
     </row>
     <row r="172" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B172" s="16" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C172" s="17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D172" s="18">
-        <v>7.74</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="E172" s="17" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F172" s="19">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="G172" s="20">
-        <v>50.71</v>
-      </c>
-      <c r="H172" s="22" t="s">
-        <v>236</v>
+        <v>1031.32</v>
+      </c>
+      <c r="H172" s="21">
+        <v>3.2987846520000002E-4</v>
       </c>
       <c r="I172" s="20">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="J172" s="15" t="s">
         <v>13</v>
@@ -6451,36 +6578,57 @@
     </row>
     <row r="173" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B173" s="16" t="s">
-        <v>13</v>
+        <v>241</v>
+      </c>
+      <c r="C173" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D173" s="18">
+        <v>7.63</v>
+      </c>
+      <c r="E173" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F173" s="19">
+        <v>100</v>
+      </c>
+      <c r="G173" s="20">
+        <v>1025.31</v>
+      </c>
+      <c r="H173" s="21">
+        <v>3.2795610399999998E-4</v>
+      </c>
+      <c r="I173" s="20">
+        <v>6.48</v>
       </c>
       <c r="J173" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="174" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="C174" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D174" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E174" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G174" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H174" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I174" s="13" t="s">
-        <v>13</v>
+      <c r="B174" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C174" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D174" s="18">
+        <v>7.95</v>
+      </c>
+      <c r="E174" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F174" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G174" s="20">
+        <v>1020.21</v>
+      </c>
+      <c r="H174" s="21">
+        <v>3.263248158E-4</v>
+      </c>
+      <c r="I174" s="20">
+        <v>7.03</v>
       </c>
       <c r="J174" s="15" t="s">
         <v>13</v>
@@ -6488,36 +6636,57 @@
     </row>
     <row r="175" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B175" s="16" t="s">
-        <v>13</v>
+        <v>61</v>
+      </c>
+      <c r="C175" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D175" s="18">
+        <v>7.77</v>
+      </c>
+      <c r="E175" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F175" s="19">
+        <v>100</v>
+      </c>
+      <c r="G175" s="20">
+        <v>1017.72</v>
+      </c>
+      <c r="H175" s="21">
+        <v>3.2552836330000001E-4</v>
+      </c>
+      <c r="I175" s="20">
+        <v>6.82</v>
       </c>
       <c r="J175" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="176" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C176" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D176" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E176" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F176" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G176" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H176" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I176" s="13" t="s">
-        <v>13</v>
+      <c r="B176" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C176" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D176" s="18">
+        <v>7.54</v>
+      </c>
+      <c r="E176" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F176" s="19">
+        <v>89</v>
+      </c>
+      <c r="G176" s="20">
+        <v>902.33</v>
+      </c>
+      <c r="H176" s="21">
+        <v>2.8861966749999998E-4</v>
+      </c>
+      <c r="I176" s="20">
+        <v>6.55</v>
       </c>
       <c r="J176" s="15" t="s">
         <v>13</v>
@@ -6525,36 +6694,57 @@
     </row>
     <row r="177" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B177" s="16" t="s">
-        <v>13</v>
+        <v>55</v>
+      </c>
+      <c r="C177" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="D177" s="18">
+        <v>7.75</v>
+      </c>
+      <c r="E177" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F177" s="19">
+        <v>63</v>
+      </c>
+      <c r="G177" s="20">
+        <v>644.04999999999995</v>
+      </c>
+      <c r="H177" s="21">
+        <v>2.0600611400000001E-4</v>
+      </c>
+      <c r="I177" s="20">
+        <v>6.52</v>
       </c>
       <c r="J177" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="178" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="C178" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E178" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F178" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G178" s="13">
-        <v>117448.9</v>
-      </c>
-      <c r="H178" s="14">
-        <v>4.0313956333500003E-2</v>
-      </c>
-      <c r="I178" s="13" t="s">
-        <v>13</v>
+      <c r="B178" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C178" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D178" s="18">
+        <v>7.68</v>
+      </c>
+      <c r="E178" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F178" s="19">
+        <v>600</v>
+      </c>
+      <c r="G178" s="20">
+        <v>609.04</v>
+      </c>
+      <c r="H178" s="21">
+        <v>1.948078001E-4</v>
+      </c>
+      <c r="I178" s="20">
+        <v>6.55</v>
       </c>
       <c r="J178" s="15" t="s">
         <v>13</v>
@@ -6562,28 +6752,28 @@
     </row>
     <row r="179" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" s="16" t="s">
-        <v>243</v>
+        <v>40</v>
       </c>
       <c r="C179" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="D179" s="17" t="s">
-        <v>13</v>
+        <v>249</v>
+      </c>
+      <c r="D179" s="18">
+        <v>7.68</v>
       </c>
       <c r="E179" s="17" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="F179" s="19">
-        <v>535</v>
+        <v>500</v>
       </c>
       <c r="G179" s="20">
-        <v>52690.67</v>
+        <v>517.47</v>
       </c>
       <c r="H179" s="21">
-        <v>1.8085902631399999E-2</v>
+        <v>1.6551818000000001E-4</v>
       </c>
       <c r="I179" s="20">
-        <v>8.32</v>
+        <v>7.14</v>
       </c>
       <c r="J179" s="15" t="s">
         <v>13</v>
@@ -6591,28 +6781,28 @@
     </row>
     <row r="180" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B180" s="16" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C180" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D180" s="17" t="s">
-        <v>13</v>
+        <v>251</v>
+      </c>
+      <c r="D180" s="18">
+        <v>7.62</v>
       </c>
       <c r="E180" s="17" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="F180" s="19">
-        <v>499</v>
+        <v>20</v>
       </c>
       <c r="G180" s="20">
-        <v>40273.01</v>
+        <v>202.65</v>
       </c>
       <c r="H180" s="21">
-        <v>1.38235808642E-2</v>
+        <v>6.4819717400000005E-5</v>
       </c>
       <c r="I180" s="20">
-        <v>8.34</v>
+        <v>6.45</v>
       </c>
       <c r="J180" s="15" t="s">
         <v>13</v>
@@ -6620,28 +6810,28 @@
     </row>
     <row r="181" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B181" s="16" t="s">
-        <v>243</v>
+        <v>45</v>
       </c>
       <c r="C181" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="D181" s="17" t="s">
-        <v>13</v>
+        <v>252</v>
+      </c>
+      <c r="D181" s="18">
+        <v>6.79</v>
       </c>
       <c r="E181" s="17" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="F181" s="19">
-        <v>256</v>
+        <v>8</v>
       </c>
       <c r="G181" s="20">
-        <v>24485.22</v>
-      </c>
-      <c r="H181" s="21">
-        <v>8.4044728379000008E-3</v>
+        <v>80.709999999999994</v>
+      </c>
+      <c r="H181" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="I181" s="20">
-        <v>8.34</v>
+        <v>6.72</v>
       </c>
       <c r="J181" s="15" t="s">
         <v>13</v>
@@ -6649,35 +6839,35 @@
     </row>
     <row r="182" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B182" s="16" t="s">
-        <v>13</v>
+        <v>253</v>
+      </c>
+      <c r="C182" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D182" s="18">
+        <v>7.74</v>
+      </c>
+      <c r="E182" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F182" s="19">
+        <v>50</v>
+      </c>
+      <c r="G182" s="20">
+        <v>51.65</v>
+      </c>
+      <c r="H182" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I182" s="20">
+        <v>6.38</v>
       </c>
       <c r="J182" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="183" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="C183" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D183" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E183" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F183" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G183" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H183" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I183" s="13" t="s">
+      <c r="B183" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J183" s="15" t="s">
@@ -6685,7 +6875,28 @@
       </c>
     </row>
     <row r="184" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="16" t="s">
+      <c r="B184" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D184" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H184" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="I184" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J184" s="15" t="s">
@@ -6693,28 +6904,7 @@
       </c>
     </row>
     <row r="185" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C185" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D185" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E185" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F185" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G185" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H185" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I185" s="13" t="s">
+      <c r="B185" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J185" s="15" t="s">
@@ -6722,7 +6912,28 @@
       </c>
     </row>
     <row r="186" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="16" t="s">
+      <c r="B186" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D186" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H186" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="I186" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J186" s="15" t="s">
@@ -6730,28 +6941,7 @@
       </c>
     </row>
     <row r="187" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="C187" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D187" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E187" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F187" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G187" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H187" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I187" s="13" t="s">
+      <c r="B187" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J187" s="15" t="s">
@@ -6759,7 +6949,28 @@
       </c>
     </row>
     <row r="188" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="16" t="s">
+      <c r="B188" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D188" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188" s="13">
+        <v>106061.69</v>
+      </c>
+      <c r="H188" s="14">
+        <v>3.3924938449300002E-2</v>
+      </c>
+      <c r="I188" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J188" s="15" t="s">
@@ -6767,29 +6978,29 @@
       </c>
     </row>
     <row r="189" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="C189" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E189" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F189" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G189" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H189" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I189" s="13" t="s">
-        <v>13</v>
+      <c r="B189" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C189" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="D189" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F189" s="19">
+        <v>535</v>
+      </c>
+      <c r="G189" s="20">
+        <v>52062.1</v>
+      </c>
+      <c r="H189" s="21">
+        <v>1.6652606026200001E-2</v>
+      </c>
+      <c r="I189" s="20">
+        <v>7.76</v>
       </c>
       <c r="J189" s="15" t="s">
         <v>13</v>
@@ -6797,36 +7008,57 @@
     </row>
     <row r="190" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B190" s="16" t="s">
-        <v>13</v>
+        <v>259</v>
+      </c>
+      <c r="C190" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="D190" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E190" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F190" s="19">
+        <v>499</v>
+      </c>
+      <c r="G190" s="20">
+        <v>30517.47</v>
+      </c>
+      <c r="H190" s="21">
+        <v>9.7613312722000002E-3</v>
+      </c>
+      <c r="I190" s="20">
+        <v>7.39</v>
       </c>
       <c r="J190" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="191" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="C191" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D191" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E191" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F191" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G191" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="H191" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I191" s="13" t="s">
-        <v>13</v>
+      <c r="B191" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C191" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="D191" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E191" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F191" s="19">
+        <v>256</v>
+      </c>
+      <c r="G191" s="20">
+        <v>23482.12</v>
+      </c>
+      <c r="H191" s="21">
+        <v>7.5110011508999997E-3</v>
+      </c>
+      <c r="I191" s="20">
+        <v>7.52</v>
       </c>
       <c r="J191" s="15" t="s">
         <v>13</v>
@@ -6842,7 +7074,7 @@
     </row>
     <row r="193" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B193" s="11" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C193" s="12" t="s">
         <v>13</v>
@@ -6857,10 +7089,10 @@
         <v>13</v>
       </c>
       <c r="G193" s="13" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H193" s="14" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="I193" s="13" t="s">
         <v>13</v>
@@ -6879,7 +7111,7 @@
     </row>
     <row r="195" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B195" s="11" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="C195" s="12" t="s">
         <v>13</v>
@@ -6894,10 +7126,10 @@
         <v>13</v>
       </c>
       <c r="G195" s="13" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H195" s="14" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="I195" s="13" t="s">
         <v>13</v>
@@ -6916,7 +7148,7 @@
     </row>
     <row r="197" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="11" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C197" s="12" t="s">
         <v>13</v>
@@ -6931,10 +7163,10 @@
         <v>13</v>
       </c>
       <c r="G197" s="13" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H197" s="14" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="I197" s="13" t="s">
         <v>13</v>
@@ -6953,7 +7185,7 @@
     </row>
     <row r="199" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B199" s="11" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C199" s="12" t="s">
         <v>13</v>
@@ -6968,10 +7200,10 @@
         <v>13</v>
       </c>
       <c r="G199" s="13">
-        <v>7846.45</v>
+        <v>45364.630000000005</v>
       </c>
       <c r="H199" s="14">
-        <v>2.6932686698000002E-3</v>
+        <v>1.4510350348999999E-2</v>
       </c>
       <c r="I199" s="13" t="s">
         <v>13</v>
@@ -6982,27 +7214,6 @@
     </row>
     <row r="200" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B200" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="C200" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="D200" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E200" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="F200" s="19">
-        <v>71915.917000000001</v>
-      </c>
-      <c r="G200" s="20">
-        <v>7846.45</v>
-      </c>
-      <c r="H200" s="21">
-        <v>2.6932686698000002E-3</v>
-      </c>
-      <c r="I200" s="20" t="s">
         <v>13</v>
       </c>
       <c r="J200" s="15" t="s">
@@ -7010,7 +7221,28 @@
       </c>
     </row>
     <row r="201" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="16" t="s">
+      <c r="B201" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F201" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G201" s="13">
+        <v>45364.630000000005</v>
+      </c>
+      <c r="H201" s="14">
+        <v>1.4510350348999999E-2</v>
+      </c>
+      <c r="I201" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J201" s="15" t="s">
@@ -7018,29 +7250,29 @@
       </c>
     </row>
     <row r="202" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="C202" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D202" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E202" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F202" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G202" s="13">
-        <v>28865.55</v>
-      </c>
-      <c r="H202" s="14">
-        <v>9.9080069906E-3</v>
-      </c>
-      <c r="I202" s="13" t="s">
-        <v>13</v>
+      <c r="B202" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C202" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="D202" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E202" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F202" s="19">
+        <v>4000</v>
+      </c>
+      <c r="G202" s="20">
+        <v>18796.060000000001</v>
+      </c>
+      <c r="H202" s="21">
+        <v>6.0121159543000003E-3</v>
+      </c>
+      <c r="I202" s="20">
+        <v>6.48</v>
       </c>
       <c r="J202" s="15" t="s">
         <v>13</v>
@@ -7048,203 +7280,963 @@
     </row>
     <row r="203" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B203" s="16" t="s">
-        <v>13</v>
+        <v>271</v>
+      </c>
+      <c r="C203" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="D203" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E203" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F203" s="19">
+        <v>2000</v>
+      </c>
+      <c r="G203" s="20">
+        <v>9516.11</v>
+      </c>
+      <c r="H203" s="21">
+        <v>3.0438270975000001E-3</v>
+      </c>
+      <c r="I203" s="20">
+        <v>6.4</v>
       </c>
       <c r="J203" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="204" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B204" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="C204" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D204" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E204" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F204" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G204" s="24">
-        <v>79049.807073109783</v>
-      </c>
-      <c r="H204" s="25">
-        <v>2.7133591464243111E-2</v>
-      </c>
-      <c r="I204" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J204" s="26" t="s">
+      <c r="B204" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C204" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="D204" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F204" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G204" s="20">
+        <v>4915.43</v>
+      </c>
+      <c r="H204" s="21">
+        <v>1.5722515848999999E-3</v>
+      </c>
+      <c r="I204" s="20">
+        <v>6.28</v>
+      </c>
+      <c r="J204" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="205" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="C205" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D205" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E205" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F205" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G205" s="24">
-        <v>2913355.83707311</v>
-      </c>
-      <c r="H205" s="25">
-        <v>0.99999999999194289</v>
-      </c>
-      <c r="I205" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J205" s="26" t="s">
+      <c r="B205" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C205" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D205" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E205" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="F205" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G205" s="20">
+        <v>4840.3599999999997</v>
+      </c>
+      <c r="H205" s="21">
+        <v>1.5482396619E-3</v>
+      </c>
+      <c r="I205" s="20">
+        <v>6.44</v>
+      </c>
+      <c r="J205" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B206" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="C206" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="D206" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E206" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F206" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G206" s="20">
+        <v>4840.0600000000004</v>
+      </c>
+      <c r="H206" s="21">
+        <v>1.5481437037999999E-3</v>
+      </c>
+      <c r="I206" s="20">
+        <v>6.45</v>
+      </c>
+      <c r="J206" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B207" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="C207" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="D207" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E207" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F207" s="19">
+        <v>500</v>
+      </c>
+      <c r="G207" s="20">
+        <v>2456.61</v>
+      </c>
+      <c r="H207" s="21">
+        <v>7.8577234660000001E-4</v>
+      </c>
+      <c r="I207" s="20">
+        <v>6.26</v>
+      </c>
+      <c r="J207" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="208" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B208" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
-      <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
-    </row>
-    <row r="209" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B209" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-    </row>
-    <row r="210" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B210" s="17" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="211" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B211" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
-    </row>
-    <row r="212" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B212" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
-      <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
-      <c r="G212" s="6"/>
-      <c r="H212" s="6"/>
-    </row>
-    <row r="213" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B213" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C213" s="6"/>
-      <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="6"/>
-      <c r="H213" s="6"/>
-    </row>
-    <row r="214" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B214" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-      <c r="G214" s="6"/>
-      <c r="H214" s="6"/>
-    </row>
-    <row r="215" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B215" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
-      <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
-      <c r="G215" s="6"/>
-      <c r="H215" s="6"/>
-    </row>
-    <row r="216" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B216" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-      <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
-    </row>
-    <row r="217" spans="2:8" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C217" s="5"/>
-      <c r="D217" s="5"/>
-      <c r="E217" s="5"/>
-      <c r="F217" s="5"/>
-      <c r="G217" s="5"/>
-    </row>
-    <row r="220" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B220" s="27" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="235" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B208" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J208" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B209" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D209" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G209" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H209" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="I209" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J209" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B210" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J210" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B211" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D211" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F211" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G211" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H211" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="I211" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J211" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B212" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J212" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B213" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D213" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F213" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G213" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H213" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="I213" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J213" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B214" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J214" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B215" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D215" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F215" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G215" s="13">
+        <v>8048.08</v>
+      </c>
+      <c r="H215" s="14">
+        <v>2.5742623810000001E-3</v>
+      </c>
+      <c r="I215" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J215" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B216" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C216" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="D216" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="F216" s="19">
+        <v>71915.917000000001</v>
+      </c>
+      <c r="G216" s="20">
+        <v>8048.08</v>
+      </c>
+      <c r="H216" s="21">
+        <v>2.5742623810000001E-3</v>
+      </c>
+      <c r="I216" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J216" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J217" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D218" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F218" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G218" s="13">
+        <v>30737.18</v>
+      </c>
+      <c r="H218" s="14">
+        <v>9.8316078087000002E-3</v>
+      </c>
+      <c r="I218" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J218" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J219" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="C220" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D220" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E220" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F220" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G220" s="24">
+        <v>74318.000389478635</v>
+      </c>
+      <c r="H220" s="25">
+        <v>2.3771388037505042E-2</v>
+      </c>
+      <c r="I220" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J220" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B221" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="C221" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D221" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E221" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G221" s="24">
+        <v>3126363.5203894801</v>
+      </c>
+      <c r="H221" s="25">
+        <v>0.99999999999130418</v>
+      </c>
+      <c r="I221" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J221" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B222" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C222" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D222" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E222" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F222" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G222" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H222" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I222" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J222" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C223" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D223" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F223" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G223" s="24">
+        <v>-85000</v>
+      </c>
+      <c r="H223" s="25">
+        <v>-2.7188137094630242E-2</v>
+      </c>
+      <c r="I223" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J223" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B224" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G224" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H224" s="21">
+        <v>-3.1986043640741457E-3</v>
+      </c>
+      <c r="I224" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J224" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E225" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G225" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H225" s="21">
+        <v>-3.1986043640741457E-3</v>
+      </c>
+      <c r="I225" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J225" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="226" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B226" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E226" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F226" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G226" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H226" s="21">
+        <v>-3.1986043640741457E-3</v>
+      </c>
+      <c r="I226" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J226" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="227" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B227" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G227" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H227" s="21">
+        <v>-1.5993021820370728E-3</v>
+      </c>
+      <c r="I227" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J227" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B228" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G228" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H228" s="21">
+        <v>-3.1986043640741457E-3</v>
+      </c>
+      <c r="I228" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J228" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B229" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G229" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H229" s="21">
+        <v>-3.1986043640741457E-3</v>
+      </c>
+      <c r="I229" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J229" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G230" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H230" s="21">
+        <v>-1.5993021820370728E-3</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J230" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B231" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F231" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G231" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H231" s="21">
+        <v>-3.1986043640741457E-3</v>
+      </c>
+      <c r="I231" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J231" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D232" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E232" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G232" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H232" s="21">
+        <v>-1.5993021820370728E-3</v>
+      </c>
+      <c r="I232" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J232" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B233" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D233" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E233" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G233" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H233" s="21">
+        <v>-1.5993021820370728E-3</v>
+      </c>
+      <c r="I233" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J233" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B234" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D234" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E234" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F234" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G234" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H234" s="21">
+        <v>-1.5993021820370728E-3</v>
+      </c>
+      <c r="I234" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J234" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" s="27" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B236" s="27" t="s">
-        <v>274</v>
+        <v>13</v>
+      </c>
+      <c r="C235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I235" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="J235" s="27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B238" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
+      <c r="E238" s="3"/>
+      <c r="F238" s="3"/>
+      <c r="G238" s="3"/>
+      <c r="H238" s="3"/>
+      <c r="I238" s="3"/>
+    </row>
+    <row r="239" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B239" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
+      <c r="E239" s="3"/>
+      <c r="F239" s="3"/>
+      <c r="G239" s="3"/>
+      <c r="H239" s="3"/>
+    </row>
+    <row r="240" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="3"/>
+      <c r="G240" s="3"/>
+      <c r="H240" s="3"/>
+    </row>
+    <row r="241" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B241" s="17" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="242" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B242" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
+      <c r="E242" s="3"/>
+      <c r="F242" s="3"/>
+      <c r="G242" s="3"/>
+      <c r="H242" s="3"/>
+    </row>
+    <row r="243" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B243" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
+      <c r="E243" s="3"/>
+      <c r="F243" s="3"/>
+      <c r="G243" s="3"/>
+      <c r="H243" s="3"/>
+    </row>
+    <row r="244" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B244" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
+      <c r="E244" s="3"/>
+      <c r="F244" s="3"/>
+      <c r="G244" s="3"/>
+      <c r="H244" s="3"/>
+    </row>
+    <row r="245" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B245" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C245" s="3"/>
+      <c r="D245" s="3"/>
+      <c r="E245" s="3"/>
+      <c r="F245" s="3"/>
+      <c r="G245" s="3"/>
+      <c r="H245" s="3"/>
+    </row>
+    <row r="246" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B246" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C246" s="3"/>
+      <c r="D246" s="3"/>
+      <c r="E246" s="3"/>
+      <c r="F246" s="3"/>
+      <c r="G246" s="3"/>
+      <c r="H246" s="3"/>
+    </row>
+    <row r="247" spans="2:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B247" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+      <c r="G247" s="1"/>
+    </row>
+    <row r="250" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B250" s="28" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B265" s="28" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B246:H246"/>
+    <mergeCell ref="B247:G247"/>
+    <mergeCell ref="B240:H240"/>
+    <mergeCell ref="B242:H242"/>
+    <mergeCell ref="B243:H243"/>
+    <mergeCell ref="B244:H244"/>
+    <mergeCell ref="B245:H245"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B208:I208"/>
-    <mergeCell ref="B209:H209"/>
-    <mergeCell ref="B216:H216"/>
-    <mergeCell ref="B217:G217"/>
-    <mergeCell ref="B211:H211"/>
-    <mergeCell ref="B212:H212"/>
-    <mergeCell ref="B213:H213"/>
-    <mergeCell ref="B214:H214"/>
-    <mergeCell ref="B215:H215"/>
+    <mergeCell ref="B238:I238"/>
+    <mergeCell ref="B239:H239"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
